--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve">sku</t>
   </si>
@@ -50,6 +50,18 @@
   </si>
   <si>
     <t xml:space="preserve">CP2606160017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2606160017 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-001747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2606020003</t>
   </si>
 </sst>
 </file>
@@ -61,7 +73,7 @@
     <numFmt numFmtId="165" formatCode="0.00"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Tahoma"/>
@@ -88,6 +100,17 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -98,7 +121,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -106,6 +129,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color rgb="FFF0F0F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFF0F0F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -132,7 +166,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -141,6 +175,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -150,6 +188,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -162,6 +212,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFF0F0F0"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -276,15 +386,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultColWidth="11.74609375" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="47.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="14.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="14.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="11.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="11.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.03"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -314,20 +426,57 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="4" t="n">
         <v>948</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="5" t="n">
         <v>46190</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="5" t="n">
         <v>46196</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>953</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>46196</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>46203</v>
       </c>
     </row>
   </sheetData>

--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t xml:space="preserve">sku</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t xml:space="preserve">CP2606160017 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 10 10 10</t>
   </si>
   <si>
     <t xml:space="preserve">IP4-001747</t>
@@ -458,19 +461,19 @@
       <c r="E3" s="5" t="n">
         <v>46196</v>
       </c>
-      <c r="G3" s="8" t="n">
+      <c r="G3" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>503</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>46175</v>

--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t xml:space="preserve">sku</t>
   </si>
@@ -46,6 +46,12 @@
     <t xml:space="preserve">dc_amount</t>
   </si>
   <si>
+    <t xml:space="preserve">couponDetailCash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">couponDetailDisc</t>
+  </si>
+  <si>
     <t xml:space="preserve">SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
   </si>
   <si>
@@ -65,6 +71,9 @@
   </si>
   <si>
     <t xml:space="preserve">DC2606020003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2607030024</t>
   </si>
 </sst>
 </file>
@@ -106,14 +115,14 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -169,7 +178,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -194,7 +203,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -202,7 +211,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -286,37 +299,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -389,7 +402,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultColWidth="11.74609375" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="47.56"/>
@@ -427,16 +440,22 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>948</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>46190</v>
@@ -447,33 +466,36 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>953</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>46190</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>46196</v>
+        <v>46220</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>503</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>46175</v>
@@ -481,6 +503,32 @@
       <c r="E4" s="5" t="n">
         <v>46203</v>
       </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>953</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>46209</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>46224</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="84">
   <si>
     <t xml:space="preserve">sku</t>
   </si>
@@ -224,6 +224,54 @@
   </si>
   <si>
     <t xml:space="preserve">MNL-002270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR5-000658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR5-000661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR4-000316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR5-000635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR4-000321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR6-000453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR5-000633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR5-000654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR5-000580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR1-000617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR3-000099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR5-000680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2606250006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR5-000681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2607080016</t>
   </si>
 </sst>
 </file>
@@ -356,8 +404,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
-  <sheetFormatPr defaultColWidth="11.671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J88"/>
+  <sheetFormatPr defaultColWidth="11.65234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="47.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="14.3"/>
@@ -619,13 +667,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B14" s="4" t="n">
-        <v>1476</v>
+        <v>3780</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>46204</v>
@@ -639,13 +687,13 @@
         <v>28</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>3780</v>
+        <v>3692</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>46224</v>
@@ -653,16 +701,16 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>3692</v>
+        <v>4824</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>46224</v>
@@ -673,13 +721,13 @@
         <v>30</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>4824</v>
+        <v>4540</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>46224</v>
@@ -687,13 +735,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>4540</v>
+        <v>4879</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>46204</v>
@@ -707,10 +755,10 @@
         <v>32</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>4879</v>
+        <v>4563</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D19" s="7" t="n">
         <v>46204</v>
@@ -727,10 +775,10 @@
         <v>32</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>4563</v>
+        <v>4597</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>46204</v>
@@ -741,13 +789,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>4597</v>
+        <v>2100</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>46204</v>
@@ -758,13 +806,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2100</v>
+        <v>2293</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>46204</v>
@@ -778,33 +826,33 @@
         <v>36</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2293</v>
+        <v>2092</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>46204</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>46224</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>2092</v>
+        <v>5119</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>46219</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -812,13 +860,13 @@
         <v>37</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>5119</v>
+        <v>5164</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>46224</v>
@@ -826,13 +874,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>5164</v>
+        <v>4188</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>46204</v>
@@ -846,10 +894,10 @@
         <v>38</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>4188</v>
+        <v>4200</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>46204</v>
@@ -860,19 +908,19 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>4200</v>
+        <v>3802</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>46224</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -880,16 +928,16 @@
         <v>39</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>3802</v>
+        <v>3938</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>46209</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>46219</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -897,13 +945,13 @@
         <v>39</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>3938</v>
+        <v>3961</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>46224</v>
@@ -911,7 +959,7 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>3961</v>
@@ -923,7 +971,7 @@
         <v>46204</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>46224</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -931,27 +979,27 @@
         <v>40</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>3961</v>
+        <v>3973</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>46219</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>3973</v>
+        <v>5970</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>46209</v>
@@ -965,13 +1013,13 @@
         <v>41</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>5970</v>
+        <v>6004</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>46224</v>
@@ -979,13 +1027,13 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>6004</v>
+        <v>1334</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>46204</v>
@@ -996,16 +1044,16 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>1334</v>
+        <v>4517</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>46224</v>
@@ -1016,13 +1064,13 @@
         <v>43</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>4517</v>
+        <v>4540</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>46224</v>
@@ -1030,16 +1078,16 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>4540</v>
+        <v>1539</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>46224</v>
@@ -1047,13 +1095,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>1539</v>
+        <v>11225</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="D39" s="7" t="n">
         <v>46209</v>
@@ -1067,13 +1115,13 @@
         <v>46</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>11225</v>
+        <v>10896</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>46224</v>
@@ -1081,16 +1129,16 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>10896</v>
+        <v>5266</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>46224</v>
@@ -1101,33 +1149,33 @@
         <v>47</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>5266</v>
+        <v>5232</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>46209</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>46224</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>5232</v>
+        <v>3496</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D43" s="7" t="n">
         <v>46209</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>46219</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1135,13 +1183,13 @@
         <v>50</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>3496</v>
+        <v>3507</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>46224</v>
@@ -1149,16 +1197,16 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>3507</v>
+        <v>5664</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="E45" s="7" t="n">
         <v>46224</v>
@@ -1169,13 +1217,13 @@
         <v>51</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>5664</v>
+        <v>5618</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="E46" s="7" t="n">
         <v>46224</v>
@@ -1183,10 +1231,10 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>5618</v>
+        <v>7173</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>24</v>
@@ -1200,16 +1248,16 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>7173</v>
+        <v>11237</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="E48" s="7" t="n">
         <v>46224</v>
@@ -1220,10 +1268,10 @@
         <v>53</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>11237</v>
+        <v>11293</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>46209</v>
@@ -1234,16 +1282,16 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>11293</v>
+        <v>8399</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="E50" s="7" t="n">
         <v>46224</v>
@@ -1251,13 +1299,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>8399</v>
+        <v>6016</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D51" s="7" t="n">
         <v>46204</v>
@@ -1268,13 +1316,13 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>6016</v>
+        <v>6526</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>46204</v>
@@ -1285,16 +1333,16 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>6526</v>
+        <v>7207</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="E53" s="7" t="n">
         <v>46224</v>
@@ -1305,16 +1353,16 @@
         <v>58</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>7207</v>
+        <v>7151</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>46209</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>46224</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1322,27 +1370,27 @@
         <v>58</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>7151</v>
+        <v>7241</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>46219</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>7241</v>
+        <v>7593</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>46204</v>
@@ -1359,10 +1407,10 @@
         <v>7593</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="E57" s="7" t="n">
         <v>46224</v>
@@ -1370,10 +1418,10 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>7593</v>
+        <v>10635</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>31</v>
@@ -1387,16 +1435,16 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>10635</v>
+        <v>1759</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="E59" s="7" t="n">
         <v>46224</v>
@@ -1404,27 +1452,27 @@
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>1759</v>
+        <v>42432</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>46204</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>46224</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>42432</v>
+        <v>13242</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>18</v>
@@ -1438,10 +1486,10 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>13242</v>
+        <v>20272</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>18</v>
@@ -1452,13 +1500,16 @@
       <c r="E62" s="7" t="n">
         <v>46234</v>
       </c>
+      <c r="G62" s="2" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>20272</v>
+        <v>9566</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>18</v>
@@ -1475,10 +1526,10 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>9566</v>
+        <v>5730</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>18</v>
@@ -1492,10 +1543,10 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>5730</v>
+        <v>3391</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>18</v>
@@ -1509,19 +1560,399 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>3391</v>
+        <v>3404</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>46204</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>46234</v>
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>3360</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>46209</v>
+      </c>
+      <c r="E67" s="7" t="n">
+        <v>46219</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>3382</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>46209</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>8989</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E69" s="7" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>8921</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>12204</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E71" s="7" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>11407</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>46209</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>12133</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>46209</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>8740</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>8683</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>10726</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>10726</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E77" s="7" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>12201</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>12201</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D79" s="7" t="n">
+        <v>46209</v>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>12996</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>6458</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>6946</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E82" s="7" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>6924</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>46209</v>
+      </c>
+      <c r="E83" s="7" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>14074</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E84" s="7" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>10578</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E85" s="7" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>2565</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E86" s="7" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>2565</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E87" s="7" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>5324</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E88" s="7" t="n">
+        <v>46213</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="382">
   <si>
     <t xml:space="preserve">sku</t>
   </si>
@@ -289,6 +289,24 @@
   </si>
   <si>
     <t xml:space="preserve">MNL-002451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001414+SP2-001415+SP2-001416 +SP2-001417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2607020043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2606250004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2607100022</t>
   </si>
   <si>
     <t xml:space="preserve">tracking</t>
@@ -1272,15 +1290,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
-  <sheetFormatPr defaultColWidth="11.65234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J97"/>
+  <sheetFormatPr defaultColWidth="11.63671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="47.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="14.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="11.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.03"/>
   </cols>
@@ -3341,6 +3359,80 @@
       </c>
       <c r="H93" s="1" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>1176</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D94" s="6" t="n">
+        <v>46209</v>
+      </c>
+      <c r="E94" s="6" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>1179</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D95" s="6" t="n">
+        <v>46209</v>
+      </c>
+      <c r="E95" s="6" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>25850</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D96" s="6" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E96" s="6" t="n">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>2857</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D97" s="6" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E97" s="6" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -3360,7 +3452,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E103"/>
-  <sheetFormatPr defaultColWidth="11.74609375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.7265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.68"/>
@@ -3370,1450 +3462,1450 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="D13" s="0" t="s">
         <v>131</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="C23" s="0" t="s">
         <v>156</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="D23" s="0" t="s">
         <v>157</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="D23" s="0" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B29" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="C29" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="C29" s="0" t="s">
-        <v>166</v>
-      </c>
       <c r="D29" s="0" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
+        <v>179</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="D30" s="0" t="s">
         <v>173</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>166</v>
-      </c>
-      <c r="D30" s="0" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="C36" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="D36" s="0" t="s">
         <v>192</v>
-      </c>
-      <c r="C36" s="0" t="s">
-        <v>185</v>
-      </c>
-      <c r="D36" s="0" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="C46" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="D46" s="0" t="s">
         <v>218</v>
-      </c>
-      <c r="C46" s="0" t="s">
-        <v>211</v>
-      </c>
-      <c r="D46" s="0" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>279</v>
+      </c>
+      <c r="C67" s="0" t="s">
         <v>274</v>
       </c>
-      <c r="B67" s="0" t="s">
-        <v>273</v>
-      </c>
-      <c r="C67" s="0" t="s">
-        <v>268</v>
-      </c>
       <c r="D67" s="0" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B71" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="C71" s="0" t="s">
         <v>287</v>
       </c>
-      <c r="C71" s="0" t="s">
-        <v>281</v>
-      </c>
       <c r="D71" s="0" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>303</v>
+      </c>
+      <c r="C75" s="0" t="s">
         <v>296</v>
       </c>
-      <c r="B75" s="0" t="s">
+      <c r="D75" s="0" t="s">
         <v>297</v>
-      </c>
-      <c r="C75" s="0" t="s">
-        <v>290</v>
-      </c>
-      <c r="D75" s="0" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
+        <v>366</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>367</v>
+      </c>
+      <c r="C97" s="0" t="s">
         <v>360</v>
       </c>
-      <c r="B97" s="0" t="s">
+      <c r="D97" s="0" t="s">
         <v>361</v>
-      </c>
-      <c r="C97" s="0" t="s">
-        <v>354</v>
-      </c>
-      <c r="D97" s="0" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
+        <v>376</v>
+      </c>
+      <c r="B101" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="C101" s="0" t="s">
         <v>370</v>
       </c>
-      <c r="B101" s="0" t="s">
+      <c r="D101" s="0" t="s">
         <v>371</v>
-      </c>
-      <c r="C101" s="0" t="s">
-        <v>364</v>
-      </c>
-      <c r="D101" s="0" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -4833,7 +4925,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.74609375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.7265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="386">
   <si>
     <t xml:space="preserve">sku</t>
   </si>
@@ -303,10 +303,22 @@
     <t xml:space="preserve">MNL-002187</t>
   </si>
   <si>
+    <t xml:space="preserve">DC2606250004 CP2607100022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-002434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002387</t>
+  </si>
+  <si>
     <t xml:space="preserve">DC2606250004</t>
   </si>
   <si>
-    <t xml:space="preserve">CP2607100022</t>
+    <t xml:space="preserve">IP4-002384</t>
   </si>
   <si>
     <t xml:space="preserve">tracking</t>
@@ -1290,12 +1302,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr defaultColWidth="11.63671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="47.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="14.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.32"/>
@@ -3412,7 +3424,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
         <v>92</v>
       </c>
@@ -3428,11 +3440,79 @@
       <c r="E97" s="6" t="n">
         <v>46234</v>
       </c>
-      <c r="F97" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="G97" s="2" t="n">
         <v>69</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>11297</v>
+      </c>
+      <c r="D98" s="6" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E98" s="6" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H98" s="1" t="n">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="D99" s="6" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E99" s="6" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H99" s="1" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>2871</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D100" s="6" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E100" s="6" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H100" s="1" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="D101" s="6" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E101" s="6" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H101" s="1" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3462,1450 +3542,1450 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="D12" s="0" t="s">
         <v>135</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>130</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="C22" s="0" t="s">
         <v>160</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="D22" s="0" t="s">
         <v>161</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="D22" s="0" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="C35" s="0" t="s">
         <v>195</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="D35" s="0" t="s">
         <v>196</v>
-      </c>
-      <c r="C35" s="0" t="s">
-        <v>191</v>
-      </c>
-      <c r="D35" s="0" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="C45" s="0" t="s">
         <v>221</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="D45" s="0" t="s">
         <v>222</v>
-      </c>
-      <c r="C45" s="0" t="s">
-        <v>217</v>
-      </c>
-      <c r="D45" s="0" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="C57" s="0" t="s">
         <v>250</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="D57" s="0" t="s">
         <v>251</v>
-      </c>
-      <c r="C57" s="0" t="s">
-        <v>246</v>
-      </c>
-      <c r="D57" s="0" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="C66" s="0" t="s">
         <v>278</v>
       </c>
-      <c r="B66" s="0" t="s">
+      <c r="D66" s="0" t="s">
         <v>279</v>
-      </c>
-      <c r="C66" s="0" t="s">
-        <v>274</v>
-      </c>
-      <c r="D66" s="0" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B67" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="C67" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="D67" s="0" t="s">
         <v>279</v>
-      </c>
-      <c r="C67" s="0" t="s">
-        <v>274</v>
-      </c>
-      <c r="D67" s="0" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B70" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="C70" s="0" t="s">
         <v>291</v>
       </c>
-      <c r="C70" s="0" t="s">
-        <v>287</v>
-      </c>
       <c r="D70" s="0" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="C71" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="D71" s="0" t="s">
         <v>292</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="E71" s="0" t="s">
         <v>293</v>
-      </c>
-      <c r="C71" s="0" t="s">
-        <v>287</v>
-      </c>
-      <c r="D71" s="0" t="s">
-        <v>288</v>
-      </c>
-      <c r="E71" s="0" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
+        <v>304</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>305</v>
+      </c>
+      <c r="C74" s="0" t="s">
         <v>300</v>
       </c>
-      <c r="B74" s="0" t="s">
+      <c r="D74" s="0" t="s">
         <v>301</v>
-      </c>
-      <c r="C74" s="0" t="s">
-        <v>296</v>
-      </c>
-      <c r="D74" s="0" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
+        <v>340</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>341</v>
+      </c>
+      <c r="C86" s="0" t="s">
         <v>336</v>
       </c>
-      <c r="B86" s="0" t="s">
+      <c r="D86" s="0" t="s">
         <v>337</v>
-      </c>
-      <c r="C86" s="0" t="s">
-        <v>332</v>
-      </c>
-      <c r="D86" s="0" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
+        <v>360</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="C93" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="B93" s="0" t="s">
+      <c r="D93" s="0" t="s">
         <v>357</v>
-      </c>
-      <c r="C93" s="0" t="s">
-        <v>352</v>
-      </c>
-      <c r="D93" s="0" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
+        <v>368</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>369</v>
+      </c>
+      <c r="C96" s="0" t="s">
         <v>364</v>
       </c>
-      <c r="B96" s="0" t="s">
+      <c r="D96" s="0" t="s">
         <v>365</v>
-      </c>
-      <c r="C96" s="0" t="s">
-        <v>360</v>
-      </c>
-      <c r="D96" s="0" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="C100" s="0" t="s">
         <v>374</v>
       </c>
-      <c r="B100" s="0" t="s">
+      <c r="D100" s="0" t="s">
         <v>375</v>
-      </c>
-      <c r="C100" s="0" t="s">
-        <v>370</v>
-      </c>
-      <c r="D100" s="0" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>

--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="106">
   <si>
     <t xml:space="preserve">sku</t>
   </si>
@@ -326,6 +326,18 @@
   </si>
   <si>
     <t xml:space="preserve">MNL-002539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2606250018    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/07/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2607020114    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/07/26</t>
   </si>
 </sst>
 </file>
@@ -626,17 +638,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J105"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="47.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="20.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="12.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2402,7 +2408,7 @@
       <c r="B102" s="0" t="n">
         <v>8122</v>
       </c>
-      <c r="D102" s="3" t="n">
+      <c r="D102" s="2" t="n">
         <v>46029</v>
       </c>
       <c r="E102" s="0" t="s">
@@ -2418,6 +2424,40 @@
       </c>
       <c r="B103" s="0" t="n">
         <v>12029</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B104" s="0" t="n">
+        <v>958</v>
+      </c>
+      <c r="C104" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="E104" s="0" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B105" s="0" t="n">
+        <v>952</v>
+      </c>
+      <c r="C105" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>46180</v>
+      </c>
+      <c r="E105" s="0" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="119">
   <si>
     <t xml:space="preserve">sku</t>
   </si>
@@ -362,6 +362,21 @@
   </si>
   <si>
     <t xml:space="preserve">CP2607010042, DC2606250004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002063</t>
   </si>
 </sst>
 </file>
@@ -482,12 +497,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="47.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="29.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="20.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="11.99"/>
@@ -2367,7 +2382,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
         <v>108</v>
       </c>
@@ -2384,7 +2399,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
         <v>109</v>
       </c>
@@ -2401,7 +2416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
         <v>110</v>
       </c>
@@ -2418,7 +2433,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
         <v>112</v>
       </c>
@@ -2436,6 +2451,91 @@
       </c>
       <c r="H112" s="0" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="B113" s="0" t="n">
+        <v>7357</v>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H113" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="B114" s="0" t="n">
+        <v>5084</v>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H114" s="0" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="B115" s="0" t="n">
+        <v>5813</v>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H115" s="0" t="n">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="B116" s="0" t="n">
+        <v>4445</v>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H116" s="0" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="B117" s="0" t="n">
+        <v>3791</v>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H117" s="0" t="n">
+        <v>1314</v>
       </c>
     </row>
   </sheetData>

--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="122">
   <si>
     <t xml:space="preserve">sku</t>
   </si>
@@ -377,6 +377,15 @@
   </si>
   <si>
     <t xml:space="preserve">MNL-002063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2607170009</t>
   </si>
 </sst>
 </file>
@@ -497,7 +506,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="47.14"/>
@@ -2521,7 +2530,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
         <v>118</v>
       </c>
@@ -2536,6 +2545,40 @@
       </c>
       <c r="H117" s="0" t="n">
         <v>1314</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="B118" s="0" t="n">
+        <v>8176</v>
+      </c>
+      <c r="C118" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="B119" s="0" t="n">
+        <v>3340</v>
+      </c>
+      <c r="C119" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>46234</v>
       </c>
     </row>
   </sheetData>

--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -9,16 +9,17 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$169</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +59,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:J169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,17 +500,12 @@
           <t>CP2606160017</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>46190</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>46196</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -524,23 +521,20 @@
           <t>CP2606160017</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>46190</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>46220</v>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>12 10 10 10</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>17</v>
       </c>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -556,17 +550,12 @@
           <t>DC2606020003</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>46175</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <v>46203</v>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -582,15 +571,12 @@
           <t>CP2607030024</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="E5" s="3" t="n">
+        <v>46224</v>
+      </c>
       <c r="I5" t="n">
         <v>15</v>
       </c>
@@ -612,17 +598,12 @@
           <t>CP2606280010</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E6" s="2" t="n">
+      <c r="D6" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -638,17 +619,12 @@
           <t>CP2607030022</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="E7" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -664,17 +640,12 @@
           <t>CP2606260030</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="D8" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -690,17 +661,12 @@
           <t>CP2607020120</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="3" t="n">
         <v>46219</v>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -716,17 +682,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="D10" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -742,17 +703,12 @@
           <t>DC2606260010</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="D11" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -768,17 +724,12 @@
           <t>CP2607030022</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="D12" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -794,17 +745,12 @@
           <t>CP2606260030</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="D13" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -820,17 +766,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="D14" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -846,17 +787,12 @@
           <t>CP2607080003</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="3" t="n">
         <v>46211</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="E15" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -872,17 +808,12 @@
           <t>CP2607030020</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="E16" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -898,17 +829,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="D17" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -924,17 +850,12 @@
           <t>CP2606250018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="D18" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -950,17 +871,12 @@
           <t>CP2607020114</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="D19" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -976,17 +892,12 @@
           <t>CP2607030024</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="D20" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1002,17 +913,12 @@
           <t>CP2606250018</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="D21" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1028,17 +934,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="D22" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1054,17 +955,12 @@
           <t>CP2607080003</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E23" s="2" t="n">
+      <c r="D23" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E23" s="3" t="n">
         <v>46219</v>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1080,17 +976,12 @@
           <t>CP2607030024</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="E24" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1106,17 +997,12 @@
           <t>CP2606250018</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="D25" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1132,17 +1018,12 @@
           <t>CP2607030024</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="D26" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1158,17 +1039,12 @@
           <t>CP2606250018</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="D27" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1184,17 +1060,12 @@
           <t>CP2607020120</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D28" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" s="3" t="n">
         <v>46219</v>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1210,17 +1081,12 @@
           <t>CP2607030020</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D29" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="E29" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1236,17 +1102,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="D30" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1262,17 +1123,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E31" s="2" t="n">
+      <c r="D31" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E31" s="3" t="n">
         <v>46219</v>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1288,17 +1144,12 @@
           <t>CP2607030020</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D32" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E32" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="E32" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1314,17 +1165,12 @@
           <t>CP2607030024</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D33" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="E33" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1340,17 +1186,12 @@
           <t>CP2606250018</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="D34" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1366,17 +1207,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="D35" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1392,17 +1228,12 @@
           <t>CP2607030020</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E36" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="E36" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1418,17 +1249,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D37" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="D37" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1444,17 +1270,12 @@
           <t>DC2607030011</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D38" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E38" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="E38" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1470,17 +1291,12 @@
           <t>CP2607030024</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D39" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="E39" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1496,17 +1312,12 @@
           <t>CP2606250018</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="D40" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1522,17 +1333,12 @@
           <t>DC2607030009</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n">
+      <c r="D41" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E41" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="E41" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1548,17 +1354,12 @@
           <t>CP2607020119</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" s="3" t="n">
         <v>46219</v>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1574,17 +1375,12 @@
           <t>CP2607030020</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D43" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E43" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="E43" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1600,17 +1396,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D44" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="D44" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1626,17 +1417,12 @@
           <t>CP2607030020</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D45" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="E45" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1652,17 +1438,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="D46" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1678,17 +1459,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="D47" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1704,17 +1480,12 @@
           <t>CP2607030020</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D48" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="E48" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1730,17 +1501,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D49" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E49" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="E49" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1756,17 +1522,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="D50" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1782,17 +1543,12 @@
           <t>CP2606260030</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="D51" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1808,17 +1564,12 @@
           <t>CP2606250015</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="D52" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1834,17 +1585,12 @@
           <t>CP2607030022</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D53" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E53" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="E53" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1860,17 +1606,12 @@
           <t>CP2607020119</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n">
+      <c r="D54" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E54" s="2" t="n">
+      <c r="E54" s="3" t="n">
         <v>46219</v>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1886,17 +1627,12 @@
           <t>CP2606260030</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="D55" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1912,17 +1648,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="D56" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1938,17 +1669,12 @@
           <t>CP2607030020</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n">
+      <c r="D57" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E57" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="E57" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1964,17 +1690,12 @@
           <t>CP2607030020</t>
         </is>
       </c>
-      <c r="D58" s="2" t="n">
+      <c r="D58" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E58" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="E58" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1990,17 +1711,12 @@
           <t>DC2606260010</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="D59" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2016,17 +1732,12 @@
           <t>CP2606280010</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E60" s="2" t="n">
+      <c r="D60" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E60" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2042,17 +1753,12 @@
           <t>CP2606280010</t>
         </is>
       </c>
-      <c r="D61" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E61" s="2" t="n">
+      <c r="D61" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E61" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2068,19 +1774,15 @@
           <t>CP2606280010</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E62" s="2" t="n">
+      <c r="D62" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E62" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
         <v>500</v>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2096,17 +1798,12 @@
           <t>CP2606280010</t>
         </is>
       </c>
-      <c r="D63" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E63" s="2" t="n">
+      <c r="D63" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E63" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2122,17 +1819,12 @@
           <t>CP2606280010</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E64" s="2" t="n">
+      <c r="D64" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E64" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2148,17 +1840,12 @@
           <t>CP2606280010</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E65" s="2" t="n">
+      <c r="D65" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E65" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2174,17 +1861,12 @@
           <t>CP2606250018</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E66" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+      <c r="D66" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2200,17 +1882,12 @@
           <t>CP2607020114</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n">
+      <c r="D67" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="E67" s="3" t="n">
         <v>46219</v>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2226,17 +1903,12 @@
           <t>CP2607030024</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n">
+      <c r="D68" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E68" s="2" t="n">
+      <c r="E68" s="3" t="n">
         <v>46219</v>
       </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2252,17 +1924,12 @@
           <t>CP2606250018</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E69" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="D69" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2278,17 +1945,12 @@
           <t>CP2607030024</t>
         </is>
       </c>
-      <c r="D70" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="D70" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2304,17 +1966,12 @@
           <t>CP2606250018</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E71" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="D71" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2330,17 +1987,12 @@
           <t>CP2607020114</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n">
+      <c r="D72" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E72" s="2" t="n">
+      <c r="E72" s="3" t="n">
         <v>46219</v>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2356,17 +2008,12 @@
           <t>CP2607030024</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n">
+      <c r="D73" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E73" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+      <c r="E73" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2382,17 +2029,12 @@
           <t>CP2606250018</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+      <c r="D74" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2408,17 +2050,12 @@
           <t>CP2607030024</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E75" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+      <c r="D75" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2434,17 +2071,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E76" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+      <c r="D76" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2460,17 +2092,12 @@
           <t>CP2607030020</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E77" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+      <c r="D77" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2486,17 +2113,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+      <c r="D78" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2512,17 +2134,12 @@
           <t>CP2607030020</t>
         </is>
       </c>
-      <c r="D79" s="2" t="n">
+      <c r="D79" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E79" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+      <c r="E79" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2538,17 +2155,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+      <c r="D80" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2564,17 +2176,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D81" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="D81" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2590,17 +2197,12 @@
           <t>CP2606260026</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E82" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
+      <c r="D82" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2616,17 +2218,12 @@
           <t>CP2607030020</t>
         </is>
       </c>
-      <c r="D83" s="2" t="n">
+      <c r="D83" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E83" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+      <c r="E83" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2642,17 +2239,12 @@
           <t>CP2606260030</t>
         </is>
       </c>
-      <c r="D84" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+      <c r="D84" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2668,17 +2260,12 @@
           <t>CP2606260030</t>
         </is>
       </c>
-      <c r="D85" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E85" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+      <c r="D85" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2694,17 +2281,12 @@
           <t>DC2606250006</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+      <c r="D86" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2720,17 +2302,12 @@
           <t>DC2606250006</t>
         </is>
       </c>
-      <c r="D87" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E87" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+      <c r="D87" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2746,19 +2323,15 @@
           <t>CP2607080016</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n">
+      <c r="D88" s="3" t="n">
         <v>46210</v>
       </c>
-      <c r="E88" s="2" t="n">
+      <c r="E88" s="3" t="n">
         <v>46213</v>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
         <v>149</v>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2774,17 +2347,12 @@
           <t>DC2607030009</t>
         </is>
       </c>
-      <c r="D89" s="2" t="n">
+      <c r="D89" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E89" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+      <c r="E89" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2800,17 +2368,12 @@
           <t>CP2606280010</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E90" s="2" t="n">
+      <c r="D90" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E90" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2821,20 +2384,15 @@
       <c r="B91" t="n">
         <v>2784</v>
       </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E91" s="2" t="n">
+      <c r="D91" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E91" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>20</v>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2850,17 +2408,12 @@
           <t>CP2606280010</t>
         </is>
       </c>
-      <c r="D92" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E92" s="2" t="n">
+      <c r="D92" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E92" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2871,20 +2424,15 @@
       <c r="B93" t="n">
         <v>13740</v>
       </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E93" s="2" t="n">
+      <c r="D93" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E93" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>4</v>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2900,17 +2448,12 @@
           <t>DC2607020043</t>
         </is>
       </c>
-      <c r="D94" s="2" t="n">
+      <c r="D94" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E94" s="2" t="n">
+      <c r="E94" s="3" t="n">
         <v>46219</v>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2926,17 +2469,12 @@
           <t>DC2607030009</t>
         </is>
       </c>
-      <c r="D95" s="2" t="n">
+      <c r="D95" s="3" t="n">
         <v>46209</v>
       </c>
-      <c r="E95" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+      <c r="E95" s="3" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2952,17 +2490,12 @@
           <t>CP2606280010</t>
         </is>
       </c>
-      <c r="D96" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E96" s="2" t="n">
+      <c r="D96" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E96" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2978,19 +2511,15 @@
           <t>DC2606250004 CP2607100022</t>
         </is>
       </c>
-      <c r="D97" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E97" s="2" t="n">
+      <c r="D97" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E97" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
         <v>69</v>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3001,20 +2530,15 @@
       <c r="B98" t="n">
         <v>11297</v>
       </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E98" s="2" t="n">
+      <c r="D98" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E98" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>1510</v>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3025,20 +2549,15 @@
       <c r="B99" t="n">
         <v>99</v>
       </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E99" s="2" t="n">
+      <c r="D99" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E99" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>120</v>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3054,19 +2573,15 @@
           <t>DC2606250004</t>
         </is>
       </c>
-      <c r="D100" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E100" s="2" t="n">
+      <c r="D100" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E100" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>15</v>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3077,20 +2592,15 @@
       <c r="B101" t="n">
         <v>109</v>
       </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E101" s="2" t="n">
+      <c r="D101" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E101" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>40</v>
       </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3101,8 +2611,7 @@
       <c r="B102" t="n">
         <v>8122</v>
       </c>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" s="2" t="n">
+      <c r="D102" s="3" t="n">
         <v>46029</v>
       </c>
       <c r="E102" t="inlineStr">
@@ -3110,13 +2619,9 @@
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>494</v>
       </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3127,18 +2632,12 @@
       <c r="B103" t="n">
         <v>12029</v>
       </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E103" s="2" t="n">
+      <c r="D103" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E103" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3154,7 +2653,7 @@
           <t xml:space="preserve">CP2606250018    </t>
         </is>
       </c>
-      <c r="D104" s="2" t="n">
+      <c r="D104" s="3" t="n">
         <v>46029</v>
       </c>
       <c r="E104" t="inlineStr">
@@ -3162,11 +2661,6 @@
           <t>21/07/26</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3182,7 +2676,7 @@
           <t xml:space="preserve">CP2607020114    </t>
         </is>
       </c>
-      <c r="D105" s="2" t="n">
+      <c r="D105" s="3" t="n">
         <v>46180</v>
       </c>
       <c r="E105" t="inlineStr">
@@ -3190,11 +2684,6 @@
           <t>16/07/26</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3205,20 +2694,15 @@
       <c r="B106" t="n">
         <v>1135</v>
       </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E106" s="2" t="n">
+      <c r="D106" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E106" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>755</v>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3229,20 +2713,15 @@
       <c r="B107" t="n">
         <v>8490</v>
       </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E107" s="2" t="n">
+      <c r="D107" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E107" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>126</v>
       </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3258,17 +2737,12 @@
           <t>CP2607150011</t>
         </is>
       </c>
-      <c r="D108" s="2" t="n">
+      <c r="D108" s="3" t="n">
         <v>46216</v>
       </c>
-      <c r="E108" s="2" t="n">
+      <c r="E108" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3279,20 +2753,15 @@
       <c r="B109" t="n">
         <v>5190</v>
       </c>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E109" s="2" t="n">
+      <c r="D109" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E109" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>200</v>
       </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3303,20 +2772,15 @@
       <c r="B110" t="n">
         <v>3364</v>
       </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E110" s="2" t="n">
+      <c r="D110" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E110" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>1</v>
       </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3332,17 +2796,12 @@
           <t xml:space="preserve">CP2606280010    </t>
         </is>
       </c>
-      <c r="D111" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E111" s="2" t="n">
+      <c r="D111" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E111" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3358,19 +2817,15 @@
           <t>CP2607010042, DC2606250004</t>
         </is>
       </c>
-      <c r="D112" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E112" s="2" t="n">
+      <c r="D112" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E112" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>1</v>
       </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3381,20 +2836,15 @@
       <c r="B113" t="n">
         <v>7357</v>
       </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E113" s="2" t="n">
+      <c r="D113" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E113" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>2</v>
       </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3405,20 +2855,15 @@
       <c r="B114" t="n">
         <v>5084</v>
       </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E114" s="2" t="n">
+      <c r="D114" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E114" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>560</v>
       </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3429,20 +2874,15 @@
       <c r="B115" t="n">
         <v>5813</v>
       </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E115" s="2" t="n">
+      <c r="D115" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E115" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>1310</v>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3453,20 +2893,15 @@
       <c r="B116" t="n">
         <v>4445</v>
       </c>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E116" s="2" t="n">
+      <c r="D116" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E116" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>62</v>
       </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3477,20 +2912,15 @@
       <c r="B117" t="n">
         <v>3791</v>
       </c>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E117" s="2" t="n">
+      <c r="D117" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E117" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>1314</v>
       </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3506,17 +2936,12 @@
           <t>CP2606280010</t>
         </is>
       </c>
-      <c r="D118" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E118" s="2" t="n">
+      <c r="D118" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E118" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3532,17 +2957,12 @@
           <t>CP2607170009</t>
         </is>
       </c>
-      <c r="D119" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E119" s="2" t="n">
+      <c r="D119" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E119" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3553,14 +2973,6 @@
       <c r="B120" t="n">
         <v>2483</v>
       </c>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3571,14 +2983,6 @@
       <c r="B121" t="n">
         <v>1292</v>
       </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3589,14 +2993,6 @@
       <c r="B122" t="n">
         <v>315</v>
       </c>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3607,14 +3003,6 @@
       <c r="B123" t="n">
         <v>143</v>
       </c>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3625,14 +3013,6 @@
       <c r="B124" t="n">
         <v>1275</v>
       </c>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3643,14 +3023,6 @@
       <c r="B125" t="n">
         <v>1351</v>
       </c>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3661,16 +3033,439 @@
       <c r="B126" t="n">
         <v>137</v>
       </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MNL-002438</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>PR5-000671</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>15739</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>MNL-002243</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>3256</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>SWP-000454</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>2990</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>MNL-002514</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>5605</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>MNL-002455</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>5155</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>SWP-000455</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>IP4-002133</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>SP1-000908</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>SP4-000196</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>MNL-002420</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>MNL-002319</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>5223</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>PR6-000277</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>5046</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>PR5-000670</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>10474</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>PR2-000600</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>3994</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>PR5-000658</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>PR5-000631</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>PR5-000673</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>7031</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>IP4-002048</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>IP2-000237</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>3257</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>PR5-000627</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>2897</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ME6-000902</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>MNL-002447</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>8252</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>PR1-000584</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>MS4-000775</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>4390</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>MNL-002025</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>10717</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>PR5-000582</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>GMA-000928</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>MS4-000939</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>4890</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>SP1-001210</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>PR1-000617</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>13939</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>MNL-002412</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>PR5-000646</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>MNL-002195</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>3087</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>IP7-000842</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>SP2-001799+SP2-001800+SP2-001801+SP2-001802</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>MNL-002471</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>3673</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$J$122</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$J$547</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="428">
   <si>
     <t xml:space="preserve">sku</t>
   </si>
@@ -265,24 +265,36 @@
     <t xml:space="preserve">CP2608080002</t>
   </si>
   <si>
+    <t xml:space="preserve">DC2608110007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR5-000580</t>
+  </si>
+  <si>
     <t xml:space="preserve">MNL-002536</t>
   </si>
   <si>
+    <t xml:space="preserve">ใส่ยับ</t>
+  </si>
+  <si>
     <t xml:space="preserve">MNL-002531</t>
   </si>
   <si>
+    <t xml:space="preserve">ไม่มีใส่ ได้เลย</t>
+  </si>
+  <si>
     <t xml:space="preserve">MNL-002416</t>
   </si>
   <si>
     <t xml:space="preserve">MNL-002537</t>
   </si>
   <si>
+    <t xml:space="preserve">DC2607300001</t>
+  </si>
+  <si>
     <t xml:space="preserve">MNL-002297</t>
   </si>
   <si>
-    <t xml:space="preserve">DC2607300001</t>
-  </si>
-  <si>
     <t xml:space="preserve">MNL-002229</t>
   </si>
   <si>
@@ -421,16 +433,880 @@
     <t xml:space="preserve">CO6-011514</t>
   </si>
   <si>
+    <t xml:space="preserve">CP2607090003 CP2608010004</t>
+  </si>
+  <si>
     <t xml:space="preserve">CO6-011696</t>
   </si>
   <si>
-    <t xml:space="preserve">CP2607090003 CP2608010004</t>
-  </si>
-  <si>
     <t xml:space="preserve">CO3-001033</t>
   </si>
   <si>
     <t xml:space="preserve">CO3-001079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aim 15/08/69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2608110015 CP2608130030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2607300001 CP2608140024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2607300021  CP2607300035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2607300001    CP2608140028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2607300021 CP2608140028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2607300021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2607300001    CP2608140021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2607300021    CP2607300035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2608140025    CP2607300018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2607300001    CP2607300046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2607300001    CP2608050012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2607300001     CP2608140027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2607300001    CP2608140027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2607300001    CP2608130025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2607300001    CP2607300018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2607300018    CP2608140025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2607300001    CP2607310059    CP2608140021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2607300001    CP2607310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2607300001    CP2608140003  CP2608140021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2607300001    CP2608140003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2607300001    CP2608140013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2608110015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR2-000495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2608130029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR6-000223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2608130020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2608140003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2608130023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2608130020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2608130033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2608130007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2608130024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2607220019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2607220014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2608050024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2608130006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2608080003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001749+SP2-001615+SP2-001616+SP2-001617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2608110014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001607+SP2-001754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001778+SP2-001779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001858+SP2-001859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO6-011770</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-001886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS2-000892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW2-000418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-001821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-002048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2607300001 CP2608140003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2608140021 DC2607300001 CP2608140003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001678+SP2-001679+SP2-001680+SP2-001681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMK-001649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME6-000961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWP-000455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS6-000209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001753+SP2-001755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS6-000228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OE3-000289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NW2-000066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP2-000384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP1-001578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-001129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FN4-000398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW1-000194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PW1-000639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMC-000025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMC-000029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NWW-000735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PW1-000528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS2-000739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-001899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS1-000547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FN4-000312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4-000825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMJ-000212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMP-000517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-002383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMS-000132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMS-000103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMSP-000003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME6-000902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMM-000240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4-000931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO3-001064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR6-001737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWP-000421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-002304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMS-000128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NWW-000853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME6-000957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME6-000952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMSR-000011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001696+SP2-001697+SP2-001698+SP2-001699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4-000939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO6-011293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMH-000522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-002322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME6-000926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NWW-000787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP7-001309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW1-000195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME6-000901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP4-000302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMK-001818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC2-001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR1-000617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP7-000779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FN4-000327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-001743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-002175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4-000778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS2-000989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PW1-000651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME1-001011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMS-000154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP2-000392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMS-000104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-002433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001869+SP2-001870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMA-002346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-001747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FN4-000414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VD3-000275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4-000932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME6-000865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NWC-000120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OE3-000230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OE3-000229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-002255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS6-000266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4-000837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FN4-000372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS2-000819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP4-000196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME1-001277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-002403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO6-011811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4-000783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMK-001820</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001799+SP2-001800+SP2-001801+SP2-001802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP2-000253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VD3-000272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FN4-000374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME6-001021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CU2-000510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-002178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP7-001308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP1-000908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP7-000731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FN4-000326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PW1-000405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS1-000565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMA-000449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CU2-000439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS6-000263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS2-000845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMH-000885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP7-001020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NW2-000083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP2-000239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001414+SP2-001415+SP2-001416+SP2-001417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR6-001659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO9-000240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO2-003809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEI-000130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO6-011294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO6-011407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMC-000057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP1-001113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4-000933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NW2-000068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMS-000060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO6-011526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS2-000754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO6-011684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4-000847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-002454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO6-011614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MD3-000260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4-000843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMS-000148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP2-000241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO6-010744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME6-000962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FN4-000295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMS-000173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS2-000983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR6-001742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS2-000818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO6-011803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4-000782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4-000839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR6-001835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME6-000994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO6-011541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4-001059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PW1-000501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO6-011117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS6-000289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMS-000167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4-000775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMP-000344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMM-000794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO3-001065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMSR-000005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR6-001790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-002172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWP-000454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMM-000258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS6-000284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS2-001007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NW2-000086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO6-011566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMH-000879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP2-000385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS6-000172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP1-001445+SP1-001446+SP1-001447+SP1-001448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO8-001044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP7-001215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMP-000346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMH-000884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TS9-000263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4-000841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO6-011776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO6-011779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO3-001063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO6-011727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP7-001216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4-000973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-001717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-002455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-001949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FN4-000335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP2-001803+SP2-001804+SP2-001805+SP2-001806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VD3-000242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS2-000861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP4-002463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMH-000889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEI-000129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS2-000003</t>
   </si>
 </sst>
 </file>
@@ -570,10 +1446,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J155"/>
+  <dimension ref="A1:J547"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="20.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26.95"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -608,7 +1484,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
         <v>10</v>
       </c>
@@ -619,7 +1495,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
         <v>10</v>
       </c>
@@ -630,7 +1506,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>13</v>
       </c>
@@ -647,7 +1523,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>13</v>
       </c>
@@ -664,7 +1540,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>14</v>
       </c>
@@ -681,7 +1557,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>14</v>
       </c>
@@ -698,7 +1574,7 @@
         <v>46251</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>14</v>
       </c>
@@ -715,7 +1591,7 @@
         <v>46251</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>14</v>
       </c>
@@ -732,7 +1608,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>17</v>
       </c>
@@ -749,7 +1625,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>17</v>
       </c>
@@ -766,7 +1642,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>17</v>
       </c>
@@ -783,7 +1659,7 @@
         <v>46242</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>10</v>
       </c>
@@ -800,7 +1676,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
         <v>10</v>
       </c>
@@ -817,7 +1693,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
         <v>19</v>
       </c>
@@ -834,7 +1710,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
         <v>19</v>
       </c>
@@ -851,7 +1727,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
         <v>22</v>
       </c>
@@ -868,7 +1744,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
         <v>22</v>
       </c>
@@ -885,7 +1761,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
         <v>23</v>
       </c>
@@ -902,7 +1778,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
         <v>23</v>
       </c>
@@ -919,7 +1795,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
         <v>24</v>
       </c>
@@ -936,7 +1812,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
         <v>24</v>
       </c>
@@ -953,7 +1829,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
         <v>25</v>
       </c>
@@ -970,7 +1846,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
         <v>25</v>
       </c>
@@ -987,7 +1863,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
         <v>28</v>
       </c>
@@ -1004,7 +1880,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
         <v>28</v>
       </c>
@@ -1021,7 +1897,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
         <v>29</v>
       </c>
@@ -1038,7 +1914,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
         <v>29</v>
       </c>
@@ -1055,7 +1931,7 @@
         <v>46251</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
         <v>29</v>
       </c>
@@ -1072,7 +1948,7 @@
         <v>46251</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
         <v>29</v>
       </c>
@@ -1089,7 +1965,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
         <v>32</v>
       </c>
@@ -1106,7 +1982,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
         <v>32</v>
       </c>
@@ -1123,7 +1999,7 @@
         <v>46251</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
         <v>32</v>
       </c>
@@ -1140,7 +2016,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
         <v>33</v>
       </c>
@@ -1157,7 +2033,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
         <v>33</v>
       </c>
@@ -1174,7 +2050,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
         <v>34</v>
       </c>
@@ -1191,7 +2067,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
         <v>34</v>
       </c>
@@ -1208,7 +2084,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
         <v>37</v>
       </c>
@@ -1225,7 +2101,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
         <v>37</v>
       </c>
@@ -1242,7 +2118,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
         <v>40</v>
       </c>
@@ -1259,7 +2135,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
         <v>40</v>
       </c>
@@ -1276,8 +2152,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
         <v>43</v>
       </c>
@@ -1294,7 +2169,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
         <v>43</v>
       </c>
@@ -1311,7 +2186,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
         <v>44</v>
       </c>
@@ -1328,7 +2203,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
         <v>44</v>
       </c>
@@ -1345,7 +2220,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
         <v>37</v>
       </c>
@@ -1362,7 +2237,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
         <v>45</v>
       </c>
@@ -1379,7 +2254,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
         <v>46</v>
       </c>
@@ -1396,7 +2271,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
         <v>47</v>
       </c>
@@ -1413,7 +2288,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
         <v>48</v>
       </c>
@@ -1430,7 +2305,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
         <v>50</v>
       </c>
@@ -1447,7 +2322,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
         <v>51</v>
       </c>
@@ -1464,7 +2339,7 @@
         <v>46251</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
         <v>52</v>
       </c>
@@ -1481,7 +2356,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
         <v>52</v>
       </c>
@@ -1498,7 +2373,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
         <v>53</v>
       </c>
@@ -1515,7 +2390,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
         <v>29</v>
       </c>
@@ -1532,7 +2407,7 @@
         <v>46251</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
         <v>54</v>
       </c>
@@ -1549,7 +2424,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
         <v>55</v>
       </c>
@@ -1566,7 +2441,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
         <v>51</v>
       </c>
@@ -1583,7 +2458,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
         <v>56</v>
       </c>
@@ -1600,7 +2475,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
         <v>17</v>
       </c>
@@ -1617,7 +2492,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
         <v>57</v>
       </c>
@@ -1634,7 +2509,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
         <v>19</v>
       </c>
@@ -1651,7 +2526,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
         <v>22</v>
       </c>
@@ -1668,7 +2543,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
         <v>14</v>
       </c>
@@ -1685,7 +2560,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
         <v>14</v>
       </c>
@@ -1702,7 +2577,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
         <v>23</v>
       </c>
@@ -1719,7 +2594,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
         <v>23</v>
       </c>
@@ -1736,7 +2611,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
         <v>58</v>
       </c>
@@ -1753,7 +2628,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
         <v>58</v>
       </c>
@@ -1770,7 +2645,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
         <v>33</v>
       </c>
@@ -1787,7 +2662,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
         <v>33</v>
       </c>
@@ -1804,7 +2679,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
         <v>59</v>
       </c>
@@ -1821,7 +2696,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
         <v>59</v>
       </c>
@@ -1838,7 +2713,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
         <v>29</v>
       </c>
@@ -1855,7 +2730,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
         <v>29</v>
       </c>
@@ -1872,7 +2747,7 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
         <v>53</v>
       </c>
@@ -1889,7 +2764,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
         <v>60</v>
       </c>
@@ -1906,7 +2781,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
         <v>54</v>
       </c>
@@ -1923,7 +2798,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
         <v>61</v>
       </c>
@@ -1940,7 +2815,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
         <v>62</v>
       </c>
@@ -1957,7 +2832,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
         <v>63</v>
       </c>
@@ -1974,7 +2849,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
         <v>28</v>
       </c>
@@ -1984,14 +2859,14 @@
       <c r="C84" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="D84" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E84" s="3" t="n">
+      <c r="D84" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E84" s="2" t="n">
         <v>46254</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
         <v>28</v>
       </c>
@@ -2001,14 +2876,14 @@
       <c r="C85" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="D85" s="3" t="n">
+      <c r="D85" s="2" t="n">
         <v>46241</v>
       </c>
-      <c r="E85" s="3" t="n">
+      <c r="E85" s="2" t="n">
         <v>46257</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
         <v>64</v>
       </c>
@@ -2018,14 +2893,14 @@
       <c r="C86" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="D86" s="3" t="n">
+      <c r="D86" s="2" t="n">
         <v>46241</v>
       </c>
-      <c r="E86" s="3" t="n">
+      <c r="E86" s="2" t="n">
         <v>46257</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
         <v>65</v>
       </c>
@@ -2035,14 +2910,14 @@
       <c r="C87" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="D87" s="3" t="n">
+      <c r="D87" s="2" t="n">
         <v>46241</v>
       </c>
-      <c r="E87" s="3" t="n">
+      <c r="E87" s="2" t="n">
         <v>46257</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
         <v>66</v>
       </c>
@@ -2059,7 +2934,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
         <v>34</v>
       </c>
@@ -2076,7 +2951,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
         <v>67</v>
       </c>
@@ -2093,7 +2968,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
         <v>68</v>
       </c>
@@ -2110,7 +2985,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
         <v>69</v>
       </c>
@@ -2127,7 +3002,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
         <v>70</v>
       </c>
@@ -2144,7 +3019,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
         <v>32</v>
       </c>
@@ -2161,7 +3036,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
         <v>71</v>
       </c>
@@ -2178,7 +3053,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
         <v>13</v>
       </c>
@@ -2195,7 +3070,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
         <v>72</v>
       </c>
@@ -2212,7 +3087,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
         <v>73</v>
       </c>
@@ -2229,7 +3104,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
         <v>74</v>
       </c>
@@ -2246,7 +3121,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
         <v>75</v>
       </c>
@@ -2263,7 +3138,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
         <v>76</v>
       </c>
@@ -2280,7 +3155,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
         <v>77</v>
       </c>
@@ -2297,7 +3172,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
         <v>78</v>
       </c>
@@ -2314,7 +3189,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
         <v>25</v>
       </c>
@@ -2331,534 +3206,564 @@
         <v>46249</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-    </row>
-    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-    </row>
-    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B105" s="0" t="n">
+        <v>3488</v>
+      </c>
+      <c r="C105" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="B106" s="0" t="n">
+        <v>6829</v>
+      </c>
+      <c r="C106" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B107" s="0" t="n">
         <v>8154</v>
       </c>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-    </row>
-    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B108" s="0" t="n">
+        <v>8154</v>
+      </c>
+      <c r="C108" s="0" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="B109" s="0" t="n">
         <v>5590</v>
       </c>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-    </row>
-    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="B109" s="0" t="n">
+      <c r="C109" s="0" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B110" s="0" t="n">
         <v>2850</v>
       </c>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-    </row>
-    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="B110" s="0" t="n">
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="B111" s="0" t="n">
         <v>3337</v>
       </c>
-      <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
-    </row>
-    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="B111" s="0" t="n">
+      <c r="C111" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="B112" s="0" t="n">
         <v>4097</v>
       </c>
-      <c r="C111" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D111" s="2" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E111" s="2" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="B112" s="0" t="n">
+      <c r="C112" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B113" s="0" t="n">
         <v>2450</v>
       </c>
-      <c r="C112" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="D112" s="2" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E112" s="2" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="B113" s="0" t="n">
+      <c r="C113" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B114" s="0" t="n">
         <v>3438</v>
       </c>
-      <c r="C113" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="D113" s="2" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E113" s="2" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="B114" s="0" t="n">
+      <c r="C114" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="B115" s="0" t="n">
         <v>20556</v>
-      </c>
-      <c r="C114" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="D114" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="s">
-        <v>90</v>
-      </c>
-      <c r="B115" s="0" t="n">
-        <v>3159</v>
       </c>
       <c r="C115" s="0" t="s">
         <v>91</v>
       </c>
-      <c r="D115" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D115" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B116" s="0" t="n">
+        <v>3159</v>
+      </c>
+      <c r="C116" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B117" s="0" t="n">
         <v>26961</v>
       </c>
-      <c r="C116" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="D116" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="B117" s="0" t="n">
+      <c r="C117" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="B118" s="0" t="n">
         <v>2821</v>
       </c>
-      <c r="C117" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="D117" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="B118" s="0" t="n">
+      <c r="C118" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B119" s="0" t="n">
         <v>2450</v>
       </c>
-      <c r="C118" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="D118" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="B119" s="0" t="n">
+      <c r="C119" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B120" s="0" t="n">
         <v>3413</v>
       </c>
-      <c r="C119" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="D119" s="2" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E119" s="2" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="B120" s="0" t="n">
+      <c r="C120" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="B121" s="0" t="n">
         <v>5810</v>
       </c>
-      <c r="C120" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="D120" s="2" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E120" s="2" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="B121" s="0" t="n">
+      <c r="C121" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B122" s="0" t="n">
         <v>2871</v>
       </c>
-      <c r="C121" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D121" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="B122" s="0" t="n">
+      <c r="C122" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="B123" s="0" t="n">
         <v>3673</v>
       </c>
-      <c r="C122" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="D122" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="B123" s="0" t="n">
+      <c r="C123" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="B124" s="0" t="n">
         <v>6683</v>
       </c>
-      <c r="C123" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D123" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E123" s="3" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="B124" s="0" t="n">
+      <c r="C124" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="B125" s="0" t="n">
         <v>10058</v>
       </c>
-      <c r="C124" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="D124" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="B125" s="0" t="n">
+      <c r="C125" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="B126" s="0" t="n">
         <v>2157</v>
       </c>
-      <c r="C125" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="D125" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="B126" s="0" t="n">
+      <c r="C126" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="B127" s="0" t="n">
         <v>37961</v>
       </c>
-      <c r="C126" s="0" t="s">
-        <v>106</v>
-      </c>
-      <c r="D126" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="0" t="s">
-        <v>107</v>
-      </c>
-      <c r="B127" s="0" t="n">
+      <c r="C127" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="B128" s="0" t="n">
         <v>5868</v>
       </c>
-      <c r="C127" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D127" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="0" t="s">
-        <v>108</v>
-      </c>
-      <c r="B128" s="0" t="n">
+      <c r="C128" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B129" s="0" t="n">
         <v>15330</v>
       </c>
-      <c r="C128" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D128" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="B129" s="0" t="n">
+      <c r="C129" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="B130" s="0" t="n">
         <v>1990</v>
       </c>
-      <c r="C129" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="D129" s="3" t="n">
+      <c r="C130" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="D130" s="2" t="n">
         <v>46242</v>
       </c>
-      <c r="E129" s="3" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="0" t="s">
-        <v>111</v>
-      </c>
-      <c r="B130" s="0" t="n">
-        <v>2850</v>
-      </c>
-      <c r="C130" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="D130" s="3" t="n">
-        <v>46240</v>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>46250</v>
+      <c r="E130" s="2" t="n">
+        <v>46265</v>
       </c>
       <c r="G130" s="0" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B131" s="0" t="n">
+        <v>2850</v>
+      </c>
+      <c r="C131" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>46250</v>
+      </c>
+      <c r="G131" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="B132" s="0" t="n">
         <v>8252</v>
       </c>
-      <c r="C131" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="D131" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="0" t="s">
-        <v>114</v>
-      </c>
-      <c r="B132" s="0" t="n">
+      <c r="C132" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="B133" s="0" t="n">
         <v>4097</v>
       </c>
-      <c r="C132" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D132" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="0" t="s">
-        <v>115</v>
-      </c>
-      <c r="B133" s="0" t="n">
-        <v>2652</v>
-      </c>
       <c r="C133" s="0" t="s">
-        <v>116</v>
-      </c>
-      <c r="D133" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E133" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E133" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="G133" s="0" t="n">
         <v>156</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B134" s="0" t="n">
+        <v>2652</v>
+      </c>
+      <c r="C134" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G134" s="0" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="B135" s="0" t="n">
         <v>3229</v>
       </c>
-      <c r="C134" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D134" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="B135" s="0" t="n">
-        <v>3704</v>
-      </c>
       <c r="C135" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D135" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E135" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E135" s="2" t="n">
         <v>46265</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B136" s="0" t="n">
-        <v>8140</v>
+        <v>3704</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D136" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E136" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E136" s="2" t="n">
         <v>46265</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B137" s="0" t="n">
-        <v>13428</v>
+        <v>8140</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="D137" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E137" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E137" s="2" t="n">
         <v>46265</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B138" s="0" t="n">
-        <v>2850</v>
+        <v>13428</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>122</v>
-      </c>
-      <c r="D138" s="3" t="n">
-        <v>46240</v>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>46250</v>
+        <v>91</v>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>46265</v>
       </c>
       <c r="G138" s="0" t="n">
         <v>29</v>
@@ -2866,66 +3771,106 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B139" s="0" t="n">
+        <v>2850</v>
+      </c>
+      <c r="C139" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>46250</v>
+      </c>
+      <c r="G139" s="0" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="B140" s="0" t="n">
         <v>3663</v>
       </c>
-      <c r="C139" s="0" t="s">
-        <v>124</v>
+      <c r="C140" s="0" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B142" s="0" t="n">
         <v>3210</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="D142" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E142" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E142" s="2" t="n">
         <v>46265</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B143" s="0" t="n">
-        <v>2490</v>
+        <v>3210</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>128</v>
-      </c>
-      <c r="D143" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E143" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E143" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="G143" s="0" t="n">
         <v>500</v>
       </c>
     </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="B144" s="0" t="n">
+        <v>2490</v>
+      </c>
+      <c r="C144" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G144" s="0" t="n">
+        <v>500</v>
+      </c>
+    </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B150" s="0" t="n">
         <v>31390</v>
       </c>
       <c r="C150" s="0" t="s">
-        <v>130</v>
-      </c>
-      <c r="D150" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="D150" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="E150" s="3" t="n">
+      <c r="E150" s="2" t="n">
         <v>46387</v>
       </c>
       <c r="G150" s="0" t="n">
@@ -2934,32 +3879,61 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B151" s="0" t="n">
-        <v>30690</v>
+        <v>31390</v>
+      </c>
+      <c r="C151" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>45566</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>46387</v>
+      </c>
+      <c r="G151" s="0" t="n">
+        <v>2400</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="0" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B152" s="0" t="n">
+        <v>30690</v>
+      </c>
+      <c r="C152" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="B153" s="0" t="n">
         <v>41890</v>
       </c>
-      <c r="C152" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="D152" s="3" t="n">
+      <c r="C153" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="D153" s="2" t="n">
         <v>46212</v>
       </c>
-      <c r="E152" s="3" t="n">
+      <c r="E153" s="2" t="n">
         <v>46251</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="0" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B154" s="0" t="n">
         <v>29590</v>
@@ -2976,26 +3950,4263 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B155" s="0" t="n">
-        <v>25790</v>
+        <v>29590</v>
       </c>
       <c r="C155" s="0" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>46240</v>
+        <v>46235</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>46250</v>
+        <v>46265</v>
       </c>
       <c r="G155" s="0" t="n">
         <v>24</v>
       </c>
+      <c r="H155" s="0" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="B156" s="0" t="n">
+        <v>25790</v>
+      </c>
+      <c r="C156" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>46250</v>
+      </c>
+      <c r="G156" s="0" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="B159" s="0" t="n">
+        <v>3159</v>
+      </c>
+      <c r="C159" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="B160" s="0" t="n">
+        <v>32151</v>
+      </c>
+      <c r="C160" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G160" s="0" t="n">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="B161" s="0" t="n">
+        <v>3411</v>
+      </c>
+      <c r="C161" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B162" s="0" t="n">
+        <v>3413</v>
+      </c>
+      <c r="C162" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="B163" s="0" t="n">
+        <v>5890</v>
+      </c>
+      <c r="C163" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G163" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="B164" s="0" t="n">
+        <v>2985</v>
+      </c>
+      <c r="C164" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="B165" s="0" t="n">
+        <v>10717</v>
+      </c>
+      <c r="C165" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="B166" s="0" t="n">
+        <v>13428</v>
+      </c>
+      <c r="C166" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="B167" s="0" t="n">
+        <v>3159</v>
+      </c>
+      <c r="C167" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="B168" s="0" t="n">
+        <v>3137</v>
+      </c>
+      <c r="C168" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G168" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B169" s="0" t="n">
+        <v>2434</v>
+      </c>
+      <c r="C169" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G169" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B170" s="0" t="n">
+        <v>2850</v>
+      </c>
+      <c r="C170" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G170" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="B171" s="0" t="n">
+        <v>3256</v>
+      </c>
+      <c r="C171" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="B172" s="0" t="n">
+        <v>3532</v>
+      </c>
+      <c r="C172" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G172" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B173" s="0" t="n">
+        <v>3438</v>
+      </c>
+      <c r="C173" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="B174" s="0" t="n">
+        <v>2487</v>
+      </c>
+      <c r="C174" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="B175" s="0" t="n">
+        <v>2453</v>
+      </c>
+      <c r="C175" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G175" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="B176" s="0" t="n">
+        <v>5969</v>
+      </c>
+      <c r="C176" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="B177" s="0" t="n">
+        <v>17933</v>
+      </c>
+      <c r="C177" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="B178" s="0" t="n">
+        <v>3256</v>
+      </c>
+      <c r="C178" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="B179" s="0" t="n">
+        <v>2157</v>
+      </c>
+      <c r="C179" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="B180" s="0" t="n">
+        <v>2127</v>
+      </c>
+      <c r="C180" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G180" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="B181" s="0" t="n">
+        <v>5828</v>
+      </c>
+      <c r="C181" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G181" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="B182" s="0" t="n">
+        <v>2850</v>
+      </c>
+      <c r="C182" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="B183" s="0" t="n">
+        <v>4423</v>
+      </c>
+      <c r="C183" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="B184" s="0" t="n">
+        <v>4393</v>
+      </c>
+      <c r="C184" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G184" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="B185" s="0" t="n">
+        <v>3653</v>
+      </c>
+      <c r="C185" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G185" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="B186" s="0" t="n">
+        <v>3704</v>
+      </c>
+      <c r="C186" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B187" s="0" t="n">
+        <v>2831</v>
+      </c>
+      <c r="C187" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H187" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B188" s="0" t="n">
+        <v>2850</v>
+      </c>
+      <c r="C188" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G188" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="B189" s="0" t="n">
+        <v>4070</v>
+      </c>
+      <c r="C189" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G189" s="0" t="n">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="B190" s="0" t="n">
+        <v>3724</v>
+      </c>
+      <c r="C190" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="B191" s="0" t="n">
+        <v>6790</v>
+      </c>
+      <c r="C191" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G191" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="B192" s="0" t="n">
+        <v>2782</v>
+      </c>
+      <c r="C192" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G192" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="B193" s="0" t="n">
+        <v>2821</v>
+      </c>
+      <c r="C193" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="B194" s="0" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C194" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H194" s="0" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="B195" s="0" t="n">
+        <v>5698</v>
+      </c>
+      <c r="C195" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="B196" s="0" t="n">
+        <v>2130</v>
+      </c>
+      <c r="C196" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="B197" s="0" t="n">
+        <v>2101</v>
+      </c>
+      <c r="C197" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G197" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="B198" s="0" t="n">
+        <v>2790</v>
+      </c>
+      <c r="C198" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="B199" s="0" t="n">
+        <v>2834</v>
+      </c>
+      <c r="C199" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="D199" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H199" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="B200" s="0" t="n">
+        <v>2971</v>
+      </c>
+      <c r="C200" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D200" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="B201" s="0" t="n">
+        <v>5155</v>
+      </c>
+      <c r="C201" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D201" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="B202" s="0" t="n">
+        <v>3324</v>
+      </c>
+      <c r="C202" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D202" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="0" t="s">
+        <v>179</v>
+      </c>
+      <c r="B203" s="0" t="n">
+        <v>8490</v>
+      </c>
+      <c r="C203" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="D203" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G203" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="B204" s="0" t="n">
+        <v>3627</v>
+      </c>
+      <c r="C204" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="D204" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G204" s="0" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="B205" s="0" t="n">
+        <v>4295</v>
+      </c>
+      <c r="C205" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D205" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G205" s="0" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B206" s="0" t="n">
+        <v>7020</v>
+      </c>
+      <c r="C206" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="D206" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="B207" s="0" t="n">
+        <v>4326</v>
+      </c>
+      <c r="C207" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="D207" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B208" s="0" t="n">
+        <v>2194</v>
+      </c>
+      <c r="C208" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="D208" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B209" s="0" t="n">
+        <v>4836</v>
+      </c>
+      <c r="C209" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="D209" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B210" s="0" t="n">
+        <v>3443</v>
+      </c>
+      <c r="C210" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="D210" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B211" s="0" t="n">
+        <v>4736</v>
+      </c>
+      <c r="C211" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="D211" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B212" s="0" t="n">
+        <v>5400</v>
+      </c>
+      <c r="C212" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="D212" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="B213" s="0" t="n">
+        <v>1665</v>
+      </c>
+      <c r="C213" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="D213" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B214" s="0" t="n">
+        <v>2897</v>
+      </c>
+      <c r="C214" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="D214" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="B215" s="0" t="n">
+        <v>11081</v>
+      </c>
+      <c r="C215" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="D215" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B216" s="0" t="n">
+        <v>3611</v>
+      </c>
+      <c r="C216" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D216" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G216" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B217" s="0" t="n">
+        <v>4444</v>
+      </c>
+      <c r="C217" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="D217" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="B218" s="0" t="n">
+        <v>4016</v>
+      </c>
+      <c r="C218" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="D218" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B219" s="0" t="n">
+        <v>6840</v>
+      </c>
+      <c r="C219" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="D219" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B220" s="0" t="n">
+        <v>3488</v>
+      </c>
+      <c r="C220" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="D220" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B221" s="0" t="n">
+        <v>10733</v>
+      </c>
+      <c r="C221" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="D221" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B222" s="0" t="n">
+        <v>4534</v>
+      </c>
+      <c r="C222" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="D222" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B223" s="0" t="n">
+        <v>4528</v>
+      </c>
+      <c r="C223" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="D223" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B224" s="0" t="n">
+        <v>10474</v>
+      </c>
+      <c r="C224" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="D224" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="B225" s="0" t="n">
+        <v>2171</v>
+      </c>
+      <c r="C225" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="D225" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B226" s="0" t="n">
+        <v>2520</v>
+      </c>
+      <c r="C226" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="D226" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="B227" s="0" t="n">
+        <v>5546</v>
+      </c>
+      <c r="C227" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="D227" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B228" s="0" t="n">
+        <v>7020</v>
+      </c>
+      <c r="C228" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="D228" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="B229" s="0" t="n">
+        <v>4613</v>
+      </c>
+      <c r="C229" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="D229" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B230" s="0" t="n">
+        <v>4534</v>
+      </c>
+      <c r="C230" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="D230" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B231" s="0" t="n">
+        <v>4528</v>
+      </c>
+      <c r="C231" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="D231" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="B232" s="0" t="n">
+        <v>2171</v>
+      </c>
+      <c r="C232" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="D232" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="B233" s="0" t="n">
+        <v>5546</v>
+      </c>
+      <c r="C233" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="D233" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="B234" s="0" t="n">
+        <v>1665</v>
+      </c>
+      <c r="C234" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="D234" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B235" s="0" t="n">
+        <v>3488</v>
+      </c>
+      <c r="C235" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="D235" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B236" s="0" t="n">
+        <v>2520</v>
+      </c>
+      <c r="C236" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="D236" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="B237" s="0" t="n">
+        <v>10935</v>
+      </c>
+      <c r="C237" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="D237" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="B238" s="0" t="n">
+        <v>17452</v>
+      </c>
+      <c r="C238" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="D238" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G238" s="0" t="n">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B239" s="0" t="n">
+        <v>2202</v>
+      </c>
+      <c r="C239" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="D239" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E239" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G239" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="B242" s="0" t="n">
+        <v>1183</v>
+      </c>
+      <c r="C242" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="D242" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E242" s="2" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="B243" s="0" t="n">
+        <v>1334</v>
+      </c>
+      <c r="C243" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="D243" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="B244" s="0" t="n">
+        <v>946</v>
+      </c>
+      <c r="C244" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="D244" s="2" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E244" s="2" t="n">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="B245" s="0" t="n">
+        <v>910</v>
+      </c>
+      <c r="C245" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="D245" s="2" t="n">
+        <v>46226</v>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="B246" s="0" t="n">
+        <v>943</v>
+      </c>
+      <c r="C246" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D246" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E246" s="2" t="n">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="B247" s="0" t="n">
+        <v>923</v>
+      </c>
+      <c r="C247" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D247" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E247" s="2" t="n">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="B248" s="0" t="n">
+        <v>950</v>
+      </c>
+      <c r="C248" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D248" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E248" s="2" t="n">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="B249" s="0" t="n">
+        <v>936</v>
+      </c>
+      <c r="C249" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D249" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E249" s="2" t="n">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="B250" s="0" t="n">
+        <v>932</v>
+      </c>
+      <c r="C250" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="D250" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E250" s="2" t="n">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="B251" s="0" t="n">
+        <v>981</v>
+      </c>
+      <c r="C251" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D251" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E251" s="2" t="n">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="B252" s="0" t="n">
+        <v>1408</v>
+      </c>
+      <c r="C252" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="D252" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E252" s="2" t="n">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="B253" s="0" t="n">
+        <v>1386</v>
+      </c>
+      <c r="C253" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D253" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E253" s="2" t="n">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="B254" s="0" t="n">
+        <v>1159</v>
+      </c>
+      <c r="C254" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="D254" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E254" s="2" t="n">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="B255" s="0" t="n">
+        <v>1156</v>
+      </c>
+      <c r="C255" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="D255" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E255" s="2" t="n">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="B256" s="0" t="n">
+        <v>1284</v>
+      </c>
+      <c r="C256" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="D256" s="2" t="n">
+        <v>46242</v>
+      </c>
+      <c r="E256" s="2" t="n">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="B257" s="0" t="n">
+        <v>1159</v>
+      </c>
+      <c r="C257" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D257" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E257" s="2" t="n">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="B258" s="0" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C258" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D258" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E258" s="2" t="n">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="B259" s="0" t="n">
+        <v>1270</v>
+      </c>
+      <c r="C259" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="D259" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="B260" s="0" t="n">
+        <v>1270</v>
+      </c>
+      <c r="C260" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="D260" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="B261" s="0" t="n">
+        <v>1244</v>
+      </c>
+      <c r="C261" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="D261" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="B262" s="0" t="n">
+        <v>936</v>
+      </c>
+      <c r="C262" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="D262" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="B263" s="0" t="n">
+        <v>934</v>
+      </c>
+      <c r="C263" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="D263" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="B264" s="0" t="n">
+        <v>773</v>
+      </c>
+      <c r="C264" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="D264" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>47369</v>
+      </c>
+    </row>
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="B265" s="0" t="n">
+        <v>806</v>
+      </c>
+      <c r="C265" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="D265" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="B266" s="0" t="n">
+        <v>810</v>
+      </c>
+      <c r="C266" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="D266" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A267" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="B267" s="0" t="n">
+        <v>844</v>
+      </c>
+      <c r="C267" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="D267" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A268" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="B268" s="0" t="n">
+        <v>1837</v>
+      </c>
+      <c r="C268" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="D268" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="B269" s="0" t="n">
+        <v>1769</v>
+      </c>
+      <c r="C269" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="D269" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A270" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="B270" s="0" t="n">
+        <v>69790</v>
+      </c>
+    </row>
+    <row r="271" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="B271" s="0" t="n">
+        <v>5969</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A272" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="B272" s="0" t="n">
+        <v>5890</v>
+      </c>
+    </row>
+    <row r="273" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A273" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="B273" s="0" t="n">
+        <v>31053</v>
+      </c>
+    </row>
+    <row r="274" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="B274" s="0" t="n">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="275" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="B275" s="0" t="n">
+        <v>16168</v>
+      </c>
+    </row>
+    <row r="276" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A276" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="B276" s="0" t="n">
+        <v>6025</v>
+      </c>
+    </row>
+    <row r="277" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A277" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="B277" s="0" t="n">
+        <v>5223</v>
+      </c>
+    </row>
+    <row r="278" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A278" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="B278" s="0" t="n">
+        <v>3542</v>
+      </c>
+    </row>
+    <row r="279" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A279" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="B279" s="0" t="n">
+        <v>2849</v>
+      </c>
+    </row>
+    <row r="280" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A280" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="B280" s="0" t="n">
+        <v>11690</v>
+      </c>
+    </row>
+    <row r="281" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A281" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="B281" s="0" t="n">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A282" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="B282" s="0" t="n">
+        <v>5619</v>
+      </c>
+      <c r="C282" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D282" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E282" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H282" s="0" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="283" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A283" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B283" s="0" t="n">
+        <v>15118</v>
+      </c>
+    </row>
+    <row r="284" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A284" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="B284" s="0" t="n">
+        <v>3364</v>
+      </c>
+    </row>
+    <row r="285" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A285" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="B285" s="0" t="n">
+        <v>4420</v>
+      </c>
+    </row>
+    <row r="286" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A286" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="B286" s="0" t="n">
+        <v>3411</v>
+      </c>
+    </row>
+    <row r="287" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A287" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="B287" s="0" t="n">
+        <v>6890</v>
+      </c>
+    </row>
+    <row r="288" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A288" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="B288" s="0" t="n">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="289" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="B289" s="0" t="n">
+        <v>4308</v>
+      </c>
+    </row>
+    <row r="290" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="B290" s="0" t="n">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="291" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A291" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="B291" s="0" t="n">
+        <v>7462</v>
+      </c>
+    </row>
+    <row r="292" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A292" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="B292" s="0" t="n">
+        <v>7613</v>
+      </c>
+    </row>
+    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A293" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="B293" s="0" t="n">
+        <v>7411</v>
+      </c>
+      <c r="C293" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="D293" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E293" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G293" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="294" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A294" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="B294" s="0" t="n">
+        <v>5605</v>
+      </c>
+    </row>
+    <row r="295" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A295" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="B295" s="0" t="n">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="296" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A296" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="B296" s="0" t="n">
+        <v>54264</v>
+      </c>
+    </row>
+    <row r="297" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A297" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="B297" s="0" t="n">
+        <v>3797</v>
+      </c>
+    </row>
+    <row r="298" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A298" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="B298" s="0" t="n">
+        <v>3823</v>
+      </c>
+    </row>
+    <row r="299" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A299" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="B299" s="0" t="n">
+        <v>6756</v>
+      </c>
+    </row>
+    <row r="300" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A300" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="B300" s="0" t="n">
+        <v>3585</v>
+      </c>
+    </row>
+    <row r="301" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A301" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="B301" s="0" t="n">
+        <v>10142</v>
+      </c>
+    </row>
+    <row r="302" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A302" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="B302" s="0" t="n">
+        <v>11900</v>
+      </c>
+    </row>
+    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A303" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="B303" s="0" t="n">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A304" s="0" t="s">
+        <v>230</v>
+      </c>
+      <c r="B304" s="0" t="n">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A305" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="B305" s="0" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A306" s="0" t="s">
+        <v>232</v>
+      </c>
+      <c r="B306" s="0" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A307" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="B307" s="0" t="n">
+        <v>5619</v>
+      </c>
+      <c r="C307" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D307" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E307" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H307" s="0" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A308" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="B308" s="0" t="n">
+        <v>2834</v>
+      </c>
+      <c r="C308" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="D308" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E308" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H308" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A309" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="B309" s="0" t="n">
+        <v>2790</v>
+      </c>
+      <c r="C309" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="D309" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E309" s="3" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A310" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="B310" s="0" t="n">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A311" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="B311" s="0" t="n">
+        <v>6890</v>
+      </c>
+    </row>
+    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A312" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="B312" s="0" t="n">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A313" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="B313" s="0" t="n">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A314" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="B314" s="0" t="n">
+        <v>31053</v>
+      </c>
+    </row>
+    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A315" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="B315" s="0" t="n">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A316" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="B316" s="0" t="n">
+        <v>5190</v>
+      </c>
+    </row>
+    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A317" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="B317" s="0" t="n">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A318" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="B318" s="0" t="n">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A319" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="B319" s="0" t="n">
+        <v>6290</v>
+      </c>
+    </row>
+    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A320" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="B320" s="0" t="n">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A321" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="B321" s="0" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A322" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="B322" s="0" t="n">
+        <v>15159</v>
+      </c>
+    </row>
+    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A323" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="B323" s="0" t="n">
+        <v>2790</v>
+      </c>
+    </row>
+    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A324" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="B324" s="0" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A325" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="B325" s="0" t="n">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A326" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="B326" s="0" t="n">
+        <v>5550</v>
+      </c>
+    </row>
+    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A327" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="B327" s="0" t="n">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A328" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="B328" s="0" t="n">
+        <v>38700</v>
+      </c>
+    </row>
+    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A329" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="B329" s="0" t="n">
+        <v>17800</v>
+      </c>
+    </row>
+    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A330" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="B330" s="0" t="n">
+        <v>7462</v>
+      </c>
+    </row>
+    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A331" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="B331" s="0" t="n">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A332" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="B332" s="0" t="n">
+        <v>4180</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A333" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="B333" s="0" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A334" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="B334" s="0" t="n">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A335" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="B335" s="0" t="n">
+        <v>3690</v>
+      </c>
+    </row>
+    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A336" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="B336" s="0" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A337" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="B337" s="0" t="n">
+        <v>5690</v>
+      </c>
+    </row>
+    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A338" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="B338" s="0" t="n">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A339" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B339" s="0" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A340" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="B340" s="0" t="n">
+        <v>7613</v>
+      </c>
+    </row>
+    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A341" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="B341" s="0" t="n">
+        <v>6025</v>
+      </c>
+    </row>
+    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A342" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="B342" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A343" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="B343" s="0" t="n">
+        <v>3542</v>
+      </c>
+    </row>
+    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A344" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="B344" s="0" t="n">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A345" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="B345" s="0" t="n">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A346" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="B346" s="0" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A347" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="B347" s="0" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A348" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="B348" s="0" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A349" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="B349" s="0" t="n">
+        <v>5690</v>
+      </c>
+    </row>
+    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A350" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B350" s="0" t="n">
+        <v>24600</v>
+      </c>
+    </row>
+    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A351" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="B351" s="0" t="n">
+        <v>24990</v>
+      </c>
+    </row>
+    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A352" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="B352" s="0" t="n">
+        <v>3364</v>
+      </c>
+    </row>
+    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A353" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B353" s="0" t="n">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A354" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="B354" s="0" t="n">
+        <v>5990</v>
+      </c>
+    </row>
+    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A355" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="B355" s="0" t="n">
+        <v>4120</v>
+      </c>
+    </row>
+    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A356" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="B356" s="0" t="n">
+        <v>2892</v>
+      </c>
+    </row>
+    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A357" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="B357" s="0" t="n">
+        <v>9028</v>
+      </c>
+    </row>
+    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A358" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="B358" s="0" t="n">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A359" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="B359" s="0" t="n">
+        <v>3585</v>
+      </c>
+    </row>
+    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A360" s="0" t="s">
+        <v>275</v>
+      </c>
+      <c r="B360" s="0" t="n">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A361" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B361" s="0" t="n">
+        <v>15118</v>
+      </c>
+    </row>
+    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A362" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="B362" s="0" t="n">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A363" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="B363" s="0" t="n">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A364" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="B364" s="0" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A365" s="0" t="s">
+        <v>279</v>
+      </c>
+      <c r="B365" s="0" t="n">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A366" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="B366" s="0" t="n">
+        <v>4420</v>
+      </c>
+    </row>
+    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A367" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="B367" s="0" t="n">
+        <v>4890</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A368" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="B368" s="0" t="n">
+        <v>30590</v>
+      </c>
+    </row>
+    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A369" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="B369" s="0" t="n">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A370" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="B370" s="0" t="n">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A371" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="B371" s="0" t="n">
+        <v>5619</v>
+      </c>
+    </row>
+    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A372" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="B372" s="0" t="n">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A373" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="B373" s="0" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A374" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="B374" s="0" t="n">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A375" s="0" t="s">
+        <v>287</v>
+      </c>
+      <c r="B375" s="0" t="n">
+        <v>8390</v>
+      </c>
+    </row>
+    <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A376" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="B376" s="0" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A377" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="B377" s="0" t="n">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A378" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="B378" s="0" t="n">
+        <v>54264</v>
+      </c>
+    </row>
+    <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A379" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="B379" s="0" t="n">
+        <v>4290</v>
+      </c>
+    </row>
+    <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A380" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="B380" s="0" t="n">
+        <v>3797</v>
+      </c>
+    </row>
+    <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A381" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="B381" s="0" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A382" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="B382" s="0" t="n">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A383" s="0" t="s">
+        <v>290</v>
+      </c>
+      <c r="B383" s="0" t="n">
+        <v>4090</v>
+      </c>
+    </row>
+    <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A384" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="B384" s="0" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A385" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="B385" s="0" t="n">
+        <v>13928</v>
+      </c>
+    </row>
+    <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A386" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="B386" s="0" t="n">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A387" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="B387" s="0" t="n">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A388" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="B388" s="0" t="n">
+        <v>5605</v>
+      </c>
+    </row>
+    <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A389" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="B389" s="0" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A390" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="B390" s="0" t="n">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A391" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="B391" s="0" t="n">
+        <v>5990</v>
+      </c>
+    </row>
+    <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A392" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="B392" s="0" t="n">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A393" s="0" t="s">
+        <v>299</v>
+      </c>
+      <c r="B393" s="0" t="n">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A394" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="B394" s="0" t="n">
+        <v>8990</v>
+      </c>
+    </row>
+    <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A395" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B395" s="0" t="n">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A396" s="0" t="s">
+        <v>301</v>
+      </c>
+      <c r="B396" s="0" t="n">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A397" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="B397" s="0" t="n">
+        <v>18348</v>
+      </c>
+    </row>
+    <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A398" s="0" t="s">
+        <v>303</v>
+      </c>
+      <c r="B398" s="0" t="n">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A399" s="0" t="s">
+        <v>304</v>
+      </c>
+      <c r="B399" s="0" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A400" s="0" t="s">
+        <v>305</v>
+      </c>
+      <c r="B400" s="0" t="n">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A401" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="B401" s="0" t="n">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A402" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="B402" s="0" t="n">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A403" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="B403" s="0" t="n">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A404" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="B404" s="0" t="n">
+        <v>6494</v>
+      </c>
+    </row>
+    <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A405" s="0" t="s">
+        <v>310</v>
+      </c>
+      <c r="B405" s="0" t="n">
+        <v>9290</v>
+      </c>
+    </row>
+    <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A406" s="0" t="s">
+        <v>311</v>
+      </c>
+      <c r="B406" s="0" t="n">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A407" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="B407" s="0" t="n">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A408" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="B408" s="0" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A409" s="0" t="s">
+        <v>313</v>
+      </c>
+      <c r="B409" s="0" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A410" s="0" t="s">
+        <v>314</v>
+      </c>
+      <c r="B410" s="0" t="n">
+        <v>2979</v>
+      </c>
+    </row>
+    <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A411" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="B411" s="0" t="n">
+        <v>3016</v>
+      </c>
+    </row>
+    <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A412" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="B412" s="0" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A413" s="0" t="s">
+        <v>317</v>
+      </c>
+      <c r="B413" s="0" t="n">
+        <v>7190</v>
+      </c>
+    </row>
+    <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A414" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="B414" s="0" t="n">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A415" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="B415" s="0" t="n">
+        <v>3190</v>
+      </c>
+    </row>
+    <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A416" s="0" t="s">
+        <v>319</v>
+      </c>
+      <c r="B416" s="0" t="n">
+        <v>5085</v>
+      </c>
+    </row>
+    <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A417" s="0" t="s">
+        <v>320</v>
+      </c>
+      <c r="B417" s="0" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A418" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="B418" s="0" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A419" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="B419" s="0" t="n">
+        <v>8590</v>
+      </c>
+    </row>
+    <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A420" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="B420" s="0" t="n">
+        <v>7411</v>
+      </c>
+    </row>
+    <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A421" s="0" t="s">
+        <v>323</v>
+      </c>
+      <c r="B421" s="0" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A422" s="0" t="s">
+        <v>324</v>
+      </c>
+      <c r="B422" s="0" t="n">
+        <v>19610</v>
+      </c>
+    </row>
+    <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A423" s="0" t="s">
+        <v>325</v>
+      </c>
+      <c r="B423" s="0" t="n">
+        <v>6490</v>
+      </c>
+    </row>
+    <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A424" s="0" t="s">
+        <v>326</v>
+      </c>
+      <c r="B424" s="0" t="n">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A425" s="0" t="s">
+        <v>327</v>
+      </c>
+      <c r="B425" s="0" t="n">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A426" s="0" t="s">
+        <v>328</v>
+      </c>
+      <c r="B426" s="0" t="n">
+        <v>2688</v>
+      </c>
+    </row>
+    <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A427" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="B427" s="0" t="n">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A428" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="B428" s="0" t="n">
+        <v>4770</v>
+      </c>
+    </row>
+    <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A429" s="0" t="s">
+        <v>331</v>
+      </c>
+      <c r="B429" s="0" t="n">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A430" s="0" t="s">
+        <v>332</v>
+      </c>
+      <c r="B430" s="0" t="n">
+        <v>5470</v>
+      </c>
+    </row>
+    <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A431" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="B431" s="0" t="n">
+        <v>5223</v>
+      </c>
+    </row>
+    <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A432" s="0" t="s">
+        <v>333</v>
+      </c>
+      <c r="B432" s="0" t="n">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A433" s="0" t="s">
+        <v>334</v>
+      </c>
+      <c r="B433" s="0" t="n">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A434" s="0" t="s">
+        <v>335</v>
+      </c>
+      <c r="B434" s="0" t="n">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A435" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="B435" s="0" t="n">
+        <v>4095</v>
+      </c>
+    </row>
+    <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A436" s="0" t="s">
+        <v>336</v>
+      </c>
+      <c r="B436" s="0" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A437" s="0" t="s">
+        <v>337</v>
+      </c>
+      <c r="B437" s="0" t="n">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A438" s="0" t="s">
+        <v>338</v>
+      </c>
+      <c r="B438" s="0" t="n">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A439" s="0" t="s">
+        <v>339</v>
+      </c>
+      <c r="B439" s="0" t="n">
+        <v>4590</v>
+      </c>
+    </row>
+    <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A440" s="0" t="s">
+        <v>340</v>
+      </c>
+      <c r="B440" s="0" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A441" s="0" t="s">
+        <v>341</v>
+      </c>
+      <c r="B441" s="0" t="n">
+        <v>5190</v>
+      </c>
+    </row>
+    <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A442" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="B442" s="0" t="n">
+        <v>8890</v>
+      </c>
+    </row>
+    <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A443" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B443" s="0" t="n">
+        <v>2894</v>
+      </c>
+    </row>
+    <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A444" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="B444" s="0" t="n">
+        <v>3823</v>
+      </c>
+    </row>
+    <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A445" s="0" t="s">
+        <v>342</v>
+      </c>
+      <c r="B445" s="0" t="n">
+        <v>4290</v>
+      </c>
+    </row>
+    <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A446" s="0" t="s">
+        <v>343</v>
+      </c>
+      <c r="B446" s="0" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A447" s="0" t="s">
+        <v>344</v>
+      </c>
+      <c r="B447" s="0" t="n">
+        <v>4560</v>
+      </c>
+    </row>
+    <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A448" s="0" t="s">
+        <v>345</v>
+      </c>
+      <c r="B448" s="0" t="n">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A449" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="B449" s="0" t="n">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A450" s="0" t="s">
+        <v>347</v>
+      </c>
+      <c r="B450" s="0" t="n">
+        <v>3172</v>
+      </c>
+    </row>
+    <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A451" s="0" t="s">
+        <v>348</v>
+      </c>
+      <c r="B451" s="0" t="n">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A452" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B452" s="0" t="n">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A453" s="0" t="s">
+        <v>349</v>
+      </c>
+      <c r="B453" s="0" t="n">
+        <v>30999</v>
+      </c>
+    </row>
+    <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A454" s="0" t="s">
+        <v>350</v>
+      </c>
+      <c r="B454" s="0" t="n">
+        <v>17090</v>
+      </c>
+    </row>
+    <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A455" s="0" t="s">
+        <v>351</v>
+      </c>
+      <c r="B455" s="0" t="n">
+        <v>21990</v>
+      </c>
+    </row>
+    <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A456" s="0" t="s">
+        <v>287</v>
+      </c>
+      <c r="B456" s="0" t="n">
+        <v>8999</v>
+      </c>
+    </row>
+    <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A457" s="0" t="s">
+        <v>352</v>
+      </c>
+      <c r="B457" s="0" t="n">
+        <v>10190</v>
+      </c>
+    </row>
+    <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A458" s="0" t="s">
+        <v>353</v>
+      </c>
+      <c r="B458" s="0" t="n">
+        <v>32590</v>
+      </c>
+    </row>
+    <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A459" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="B459" s="0" t="n">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A460" s="0" t="s">
+        <v>354</v>
+      </c>
+      <c r="B460" s="0" t="n">
+        <v>30090</v>
+      </c>
+    </row>
+    <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A461" s="0" t="s">
+        <v>355</v>
+      </c>
+      <c r="B461" s="0" t="n">
+        <v>28480</v>
+      </c>
+    </row>
+    <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A462" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="B462" s="0" t="n">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A463" s="0" t="s">
+        <v>357</v>
+      </c>
+      <c r="B463" s="0" t="n">
+        <v>5690</v>
+      </c>
+    </row>
+    <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A464" s="0" t="s">
+        <v>358</v>
+      </c>
+      <c r="B464" s="0" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A465" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="B465" s="0" t="n">
+        <v>11900</v>
+      </c>
+    </row>
+    <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A466" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="B466" s="0" t="n">
+        <v>4308</v>
+      </c>
+    </row>
+    <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A467" s="0" t="s">
+        <v>359</v>
+      </c>
+      <c r="B467" s="0" t="n">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A468" s="0" t="s">
+        <v>360</v>
+      </c>
+      <c r="B468" s="0" t="n">
+        <v>29490</v>
+      </c>
+    </row>
+    <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A469" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="B469" s="0" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A470" s="0" t="s">
+        <v>362</v>
+      </c>
+      <c r="B470" s="0" t="n">
+        <v>68190</v>
+      </c>
+    </row>
+    <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A471" s="0" t="s">
+        <v>363</v>
+      </c>
+      <c r="B471" s="0" t="n">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A472" s="0" t="s">
+        <v>364</v>
+      </c>
+      <c r="B472" s="0" t="n">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A473" s="0" t="s">
+        <v>365</v>
+      </c>
+      <c r="B473" s="0" t="n">
+        <v>40290</v>
+      </c>
+    </row>
+    <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A474" s="0" t="s">
+        <v>366</v>
+      </c>
+      <c r="B474" s="0" t="n">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A475" s="0" t="s">
+        <v>367</v>
+      </c>
+      <c r="B475" s="0" t="n">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A476" s="0" t="s">
+        <v>327</v>
+      </c>
+      <c r="B476" s="0" t="n">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A477" s="0" t="s">
+        <v>368</v>
+      </c>
+      <c r="B477" s="0" t="n">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A478" s="0" t="s">
+        <v>369</v>
+      </c>
+      <c r="B478" s="0" t="n">
+        <v>2958</v>
+      </c>
+    </row>
+    <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A479" s="0" t="s">
+        <v>370</v>
+      </c>
+      <c r="B479" s="0" t="n">
+        <v>20490</v>
+      </c>
+    </row>
+    <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A480" s="0" t="s">
+        <v>371</v>
+      </c>
+      <c r="B480" s="0" t="n">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A481" s="0" t="s">
+        <v>372</v>
+      </c>
+      <c r="B481" s="0" t="n">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A482" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="B482" s="0" t="n">
+        <v>2849</v>
+      </c>
+    </row>
+    <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A483" s="0" t="s">
+        <v>373</v>
+      </c>
+      <c r="B483" s="0" t="n">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A484" s="0" t="s">
+        <v>374</v>
+      </c>
+      <c r="B484" s="0" t="n">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A485" s="0" t="s">
+        <v>375</v>
+      </c>
+      <c r="B485" s="0" t="n">
+        <v>19990</v>
+      </c>
+    </row>
+    <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A486" s="0" t="s">
+        <v>376</v>
+      </c>
+      <c r="B486" s="0" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A487" s="0" t="s">
+        <v>376</v>
+      </c>
+      <c r="B487" s="0" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A488" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="B488" s="0" t="n">
+        <v>20490</v>
+      </c>
+    </row>
+    <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A489" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="B489" s="0" t="n">
+        <v>4950</v>
+      </c>
+    </row>
+    <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A490" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="B490" s="0" t="n">
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A491" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="B491" s="0" t="n">
+        <v>16999</v>
+      </c>
+    </row>
+    <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A492" s="0" t="s">
+        <v>381</v>
+      </c>
+      <c r="B492" s="0" t="n">
+        <v>2990</v>
+      </c>
+    </row>
+    <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A493" s="0" t="s">
+        <v>382</v>
+      </c>
+      <c r="B493" s="0" t="n">
+        <v>31170</v>
+      </c>
+    </row>
+    <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A494" s="0" t="s">
+        <v>383</v>
+      </c>
+      <c r="B494" s="0" t="n">
+        <v>4190</v>
+      </c>
+    </row>
+    <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A495" s="0" t="s">
+        <v>384</v>
+      </c>
+      <c r="B495" s="0" t="n">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A496" s="0" t="s">
+        <v>385</v>
+      </c>
+      <c r="B496" s="0" t="n">
+        <v>85990</v>
+      </c>
+    </row>
+    <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A497" s="0" t="s">
+        <v>386</v>
+      </c>
+      <c r="B497" s="0" t="n">
+        <v>4290</v>
+      </c>
+    </row>
+    <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A498" s="0" t="s">
+        <v>387</v>
+      </c>
+      <c r="B498" s="0" t="n">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A499" s="0" t="s">
+        <v>388</v>
+      </c>
+      <c r="B499" s="0" t="n">
+        <v>4390</v>
+      </c>
+    </row>
+    <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A500" s="0" t="s">
+        <v>389</v>
+      </c>
+      <c r="B500" s="0" t="n">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A501" s="0" t="s">
+        <v>390</v>
+      </c>
+      <c r="B501" s="0" t="n">
+        <v>4290</v>
+      </c>
+    </row>
+    <row r="502" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A502" s="0" t="s">
+        <v>391</v>
+      </c>
+      <c r="B502" s="0" t="n">
+        <v>25690</v>
+      </c>
+    </row>
+    <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A503" s="0" t="s">
+        <v>392</v>
+      </c>
+      <c r="B503" s="0" t="n">
+        <v>9280</v>
+      </c>
+    </row>
+    <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A504" s="0" t="s">
+        <v>393</v>
+      </c>
+      <c r="B504" s="0" t="n">
+        <v>16990</v>
+      </c>
+    </row>
+    <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A505" s="0" t="s">
+        <v>394</v>
+      </c>
+      <c r="B505" s="0" t="n">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A506" s="0" t="s">
+        <v>395</v>
+      </c>
+      <c r="B506" s="0" t="n">
+        <v>2980</v>
+      </c>
+    </row>
+    <row r="507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A507" s="0" t="s">
+        <v>396</v>
+      </c>
+      <c r="B507" s="0" t="n">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A508" s="0" t="s">
+        <v>397</v>
+      </c>
+      <c r="B508" s="0" t="n">
+        <v>4190</v>
+      </c>
+    </row>
+    <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A509" s="0" t="s">
+        <v>398</v>
+      </c>
+      <c r="B509" s="0" t="n">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A510" s="0" t="s">
+        <v>399</v>
+      </c>
+      <c r="B510" s="0" t="n">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A511" s="0" t="s">
+        <v>400</v>
+      </c>
+      <c r="B511" s="0" t="n">
+        <v>31190</v>
+      </c>
+    </row>
+    <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A512" s="0" t="s">
+        <v>401</v>
+      </c>
+      <c r="B512" s="0" t="n">
+        <v>2990</v>
+      </c>
+    </row>
+    <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A513" s="0" t="s">
+        <v>402</v>
+      </c>
+      <c r="B513" s="0" t="n">
+        <v>20814</v>
+      </c>
+    </row>
+    <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A514" s="0" t="s">
+        <v>403</v>
+      </c>
+      <c r="B514" s="0" t="n">
+        <v>7690</v>
+      </c>
+    </row>
+    <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A515" s="0" t="s">
+        <v>404</v>
+      </c>
+      <c r="B515" s="0" t="n">
+        <v>11673</v>
+      </c>
+    </row>
+    <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A516" s="0" t="s">
+        <v>405</v>
+      </c>
+      <c r="B516" s="0" t="n">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A517" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="B517" s="0" t="n">
+        <v>26990</v>
+      </c>
+    </row>
+    <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A518" s="0" t="s">
+        <v>406</v>
+      </c>
+      <c r="B518" s="0" t="n">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A519" s="0" t="s">
+        <v>407</v>
+      </c>
+      <c r="B519" s="0" t="n">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A520" s="0" t="s">
+        <v>408</v>
+      </c>
+      <c r="B520" s="0" t="n">
+        <v>4560</v>
+      </c>
+    </row>
+    <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A521" s="0" t="s">
+        <v>409</v>
+      </c>
+      <c r="B521" s="0" t="n">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A522" s="0" t="s">
+        <v>410</v>
+      </c>
+      <c r="B522" s="0" t="n">
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A523" s="0" t="s">
+        <v>411</v>
+      </c>
+      <c r="B523" s="0" t="n">
+        <v>23640</v>
+      </c>
+    </row>
+    <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A524" s="0" t="s">
+        <v>317</v>
+      </c>
+      <c r="B524" s="0" t="n">
+        <v>7590</v>
+      </c>
+    </row>
+    <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A525" s="0" t="s">
+        <v>412</v>
+      </c>
+      <c r="B525" s="0" t="n">
+        <v>51590</v>
+      </c>
+    </row>
+    <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A526" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="B526" s="0" t="n">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A527" s="0" t="s">
+        <v>413</v>
+      </c>
+      <c r="B527" s="0" t="n">
+        <v>26790</v>
+      </c>
+    </row>
+    <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A528" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="B528" s="0" t="n">
+        <v>5890</v>
+      </c>
+    </row>
+    <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A529" s="0" t="s">
+        <v>414</v>
+      </c>
+      <c r="B529" s="0" t="n">
+        <v>27240</v>
+      </c>
+    </row>
+    <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A530" s="0" t="s">
+        <v>415</v>
+      </c>
+      <c r="B530" s="0" t="n">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="531" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A531" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="B531" s="0" t="n">
+        <v>6756</v>
+      </c>
+    </row>
+    <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A532" s="0" t="s">
+        <v>416</v>
+      </c>
+      <c r="B532" s="0" t="n">
+        <v>3450</v>
+      </c>
+    </row>
+    <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A533" s="0" t="s">
+        <v>417</v>
+      </c>
+      <c r="B533" s="0" t="n">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A534" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="B534" s="0" t="n">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A535" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B535" s="0" t="n">
+        <v>10418</v>
+      </c>
+    </row>
+    <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A536" s="0" t="s">
+        <v>418</v>
+      </c>
+      <c r="B536" s="0" t="n">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A537" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="B537" s="0" t="n">
+        <v>10142</v>
+      </c>
+    </row>
+    <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A538" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="B538" s="0" t="n">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A539" s="0" t="s">
+        <v>420</v>
+      </c>
+      <c r="B539" s="0" t="n">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A540" s="0" t="s">
+        <v>421</v>
+      </c>
+      <c r="B540" s="0" t="n">
+        <v>2873</v>
+      </c>
+    </row>
+    <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A541" s="0" t="s">
+        <v>422</v>
+      </c>
+      <c r="B541" s="0" t="n">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A542" s="0" t="s">
+        <v>423</v>
+      </c>
+      <c r="B542" s="0" t="n">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="543" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A543" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="B543" s="0" t="n">
+        <v>2890</v>
+      </c>
+    </row>
+    <row r="544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A544" s="0" t="s">
+        <v>425</v>
+      </c>
+      <c r="B544" s="0" t="n">
+        <v>2988</v>
+      </c>
+    </row>
+    <row r="545" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A545" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="B545" s="0" t="n">
+        <v>4537</v>
+      </c>
+    </row>
+    <row r="546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A546" s="0" t="s">
+        <v>426</v>
+      </c>
+      <c r="B546" s="0" t="n">
+        <v>6090</v>
+      </c>
+    </row>
+    <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A547" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="B547" s="0" t="n">
+        <v>5490</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J122"/>
+  <autoFilter ref="A1:J547"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -4,31 +4,50 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$62</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
+      <charset val="1"/>
       <family val="2"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Cambria"/>
+      <charset val="1"/>
+      <family val="0"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -52,21 +71,58 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -423,127 +479,1605 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:J62"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="12.27" customWidth="1" style="3" min="1" max="1"/>
+    <col width="14.08" customWidth="1" style="3" min="2" max="2"/>
+    <col width="16.71" customWidth="1" style="3" min="3" max="3"/>
+    <col width="20.18" customWidth="1" style="3" min="4" max="4"/>
+    <col width="19.35" customWidth="1" style="3" min="5" max="5"/>
+    <col width="14.9" customWidth="1" style="3" min="6" max="6"/>
+    <col width="14.77" customWidth="1" style="3" min="7" max="8"/>
+    <col width="21.99" customWidth="1" style="3" min="9" max="9"/>
+    <col width="21.57" customWidth="1" style="3" min="10" max="10"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="4">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>sale_price</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>cp_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>usage_start_date</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>usage_end_date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>addtion_cp</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>oc_amount</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>dc_amount</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>couponDetailCash</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>couponDetailDisc</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1159</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CP2608130029</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1171</v>
-      </c>
-      <c r="C3" t="inlineStr">
+    <row r="2" ht="13.8" customHeight="1" s="4">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>PR6-000277</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>5046</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>CP2608130020</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="13.8" customHeight="1" s="4">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>PR2-000496</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>3713</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608130029    </t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="13.8" customHeight="1" s="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>PR2-000471</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2202</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608180005    </t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>18/8/2026</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="13.8" customHeight="1" s="4">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000635</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>8201</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608130020    </t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>14/8/2026</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="13.8" customHeight="1" s="4">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000635</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>8147</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>CP2608210032</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>23/8/2026</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>31/8/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="13.8" customHeight="1" s="4">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>PR6-000432</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>16639</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608130020    </t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>14/8/2026</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="13.8" customHeight="1" s="4">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000549</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>23929</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608130020    </t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>14/8/2026</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="13.8" customHeight="1" s="4">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000631</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1665</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>DC2608130020</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>14/8/2026</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="4">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000663</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>7695</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608130029    </t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>14/8/2026</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="4">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>PR1-000585</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>3443</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608130029    </t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>14/8/2026</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="4">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000582</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>2171</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608130029    </t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>14/8/2026</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="4">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000655</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>8235</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608130029    </t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>14/8/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="4">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000673</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>7020</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608130029    </t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>14/8/2026</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="4">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000658</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>3488</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC2608130007    </t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>14/8/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="4">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000659</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>4507</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210032    </t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>23/8/2026</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="4">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000687</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>5526</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC2608210007    </t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="4">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>PR2-000471</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>2187</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210028    </t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="4">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000582</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>2164</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>CP2608210018</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="4">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>PR6-000223</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>4317</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210028    </t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="4">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000659</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>4520</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210028    </t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>24/08/2026</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1159</v>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="4">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>PR1-000584</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1356</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>DC2608210004</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="4">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000686</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>5068</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC2608210007    </t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="4">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000627</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>2887</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210018    </t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="4">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000677</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>4034</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210018    </t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="4">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>PR6-000279</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>6396</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210028    </t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="4">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000631</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>1672</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>DC2608210004</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="4">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000655</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>8238</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210018    </t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="4">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>PR6-000436</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>10712</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210028    </t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="4">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000646</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>4464</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210018    </t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="4">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>PR1-000617</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>13899</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210021    </t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="4">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000683</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1672</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC2608210004    </t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="4">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000660</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>6125</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210028    </t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="4">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000548</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>4858</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>CP2608210018</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>24/08/26</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>08/09/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="4">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000645</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>3876</v>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210018    </t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="4">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000668</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>4690</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210018    </t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="4">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000586</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>30736</v>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210021    </t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="4">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000680</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>2514</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC2608210011    </t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="4">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>PR6-000277</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>5029</v>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210028    </t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="4">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000635</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>8181</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210028    </t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="4">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>PR4-000316</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>11244</v>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210032    </t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="4">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>PR6-000432</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>16600</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210028    </t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="4">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>PR6-000170</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>5870</v>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210018    </t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="4">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000610</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>4757</v>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>DC2608210007</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="4">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000574</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>6418</v>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210031    </t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="4">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>PR1-000584</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>1416</v>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC2608180002    </t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>18/8/2026</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="4">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>PR1-000551</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>7447</v>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210018    </t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="4">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>PR6-000453</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>12690</v>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210018    </t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="4">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000662</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>9255</v>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>CP2608210028</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="4">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000641</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>11063</v>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210021    </t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="4">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000549</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>23900</v>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210028    </t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="4">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000548</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>5073</v>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608180006    </t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>18/8/2026</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="4">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000673</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>7017</v>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210018    </t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="4">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>PR2-000495</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>4079</v>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>CP2608240002</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="4">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>PR1-000585</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>3673</v>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>CP2608210018</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>24/8/2026</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>8/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="4">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>PR6-000432</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>17452</v>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608180005    </t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="4">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>PR3-000099</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>10464</v>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210021    </t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="4">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000670</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>10986</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>CP2608180007</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="4">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000671</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>16588</v>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>DC2608210004</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="4">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000627</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>2876</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210024    </t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="4">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>PR2-000496</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>3978</v>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608240002    </t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="4">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>PR5-000547</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>4260</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP2608210018    </t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J4"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:J62"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="497">
   <si>
     <t xml:space="preserve">sku</t>
   </si>
@@ -485,6 +485,9 @@
   </si>
   <si>
     <t xml:space="preserve">MNL-002387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC2607300001 CP2608260011</t>
   </si>
   <si>
     <t xml:space="preserve">MNL-002091</t>
@@ -1650,7 +1653,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J505"/>
-  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="49.87"/>
@@ -3536,16 +3539,28 @@
       <c r="B107" s="1" t="n">
         <v>2850</v>
       </c>
+      <c r="C107" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G107" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B108" s="1" t="n">
         <v>3159</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D108" s="3" t="n">
         <v>46235</v>
@@ -3562,13 +3577,13 @@
         <v>2453</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>151</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G109" s="1" t="n">
         <v>2</v>
@@ -3576,7 +3591,7 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B110" s="1" t="n">
         <v>2713</v>
@@ -3584,7 +3599,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B111" s="1" t="n">
         <v>2870</v>
@@ -3596,12 +3611,12 @@
         <v>149</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B112" s="1" t="n">
         <v>2781</v>
@@ -3613,12 +3628,12 @@
         <v>149</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B113" s="1" t="n">
         <v>3438</v>
@@ -3630,24 +3645,24 @@
         <v>149</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B114" s="1" t="n">
         <v>3337</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>149</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G114" s="1" t="n">
         <v>276</v>
@@ -3655,7 +3670,7 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B115" s="1" t="n">
         <v>5605</v>
@@ -3667,12 +3682,12 @@
         <v>149</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B116" s="1" t="n">
         <v>5828</v>
@@ -3680,11 +3695,14 @@
       <c r="C116" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D116" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>157</v>
+      <c r="D116" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G116" s="1" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3695,13 +3713,13 @@
         <v>8490</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>151</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G117" s="1" t="n">
         <v>11</v>
@@ -3721,7 +3739,7 @@
         <v>151</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G118" s="1" t="n">
         <v>105</v>
@@ -3729,7 +3747,7 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B119" s="1" t="n">
         <v>25850</v>
@@ -3741,24 +3759,24 @@
         <v>151</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B120" s="1" t="n">
         <v>3137</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>151</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G120" s="1" t="n">
         <v>7</v>
@@ -3766,7 +3784,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B121" s="1" t="n">
         <v>5238</v>
@@ -3774,7 +3792,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B122" s="1" t="n">
         <v>2700</v>
@@ -3786,24 +3804,24 @@
         <v>149</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B123" s="1" t="n">
         <v>5568</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>151</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G123" s="1" t="n">
         <v>13</v>
@@ -3811,24 +3829,24 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B124" s="1" t="n">
         <v>3724</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>149</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B125" s="1" t="n">
         <v>2985</v>
@@ -3865,7 +3883,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B127" s="1" t="n">
         <v>3087</v>
@@ -3882,7 +3900,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B128" s="1" t="n">
         <v>5223</v>
@@ -3905,13 +3923,13 @@
         <v>2127</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>151</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G129" s="1" t="n">
         <v>2</v>
@@ -3919,7 +3937,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B130" s="1" t="n">
         <v>2763</v>
@@ -3931,7 +3949,7 @@
         <v>151</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G130" s="1" t="n">
         <v>7</v>
@@ -3939,7 +3957,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B131" s="1" t="n">
         <v>3690</v>
@@ -3951,7 +3969,7 @@
         <v>151</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G131" s="1" t="n">
         <v>21</v>
@@ -3959,7 +3977,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B132" s="1" t="n">
         <v>3823</v>
@@ -3982,7 +4000,7 @@
         <v>2955</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>98</v>
@@ -3993,7 +4011,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B134" s="1" t="n">
         <v>2187</v>
@@ -4001,13 +4019,13 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B135" s="1" t="n">
         <v>8405</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>12</v>
@@ -4024,7 +4042,7 @@
         <v>2782</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>12</v>
@@ -4038,13 +4056,13 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B137" s="1" t="n">
         <v>2834</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>12</v>
@@ -4058,13 +4076,13 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B138" s="1" t="n">
         <v>2652</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>98</v>
@@ -4078,7 +4096,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B139" s="1" t="n">
         <v>3653</v>
@@ -4098,13 +4116,13 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B140" s="1" t="n">
         <v>6790</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>12</v>
@@ -4118,7 +4136,7 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B141" s="1" t="n">
         <v>4308</v>
@@ -4138,7 +4156,7 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B142" s="1" t="n">
         <v>15330</v>
@@ -4150,12 +4168,12 @@
         <v>149</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B143" s="1" t="n">
         <v>5590</v>
@@ -4171,7 +4189,7 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B145" s="1" t="n">
         <v>15118</v>
@@ -4191,7 +4209,7 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B146" s="1" t="n">
         <v>8176</v>
@@ -4211,7 +4229,7 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B147" s="1" t="n">
         <v>3704</v>
@@ -4248,7 +4266,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B149" s="1" t="n">
         <v>3672</v>
@@ -4268,7 +4286,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B150" s="1" t="n">
         <v>8262</v>
@@ -4285,13 +4303,13 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B151" s="1" t="n">
         <v>3278</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>12</v>
@@ -4305,7 +4323,7 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B152" s="1" t="n">
         <v>2381</v>
@@ -4322,7 +4340,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B153" s="1" t="n">
         <v>3256</v>
@@ -4356,7 +4374,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B155" s="1" t="n">
         <v>9118</v>
@@ -4373,7 +4391,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B156" s="1" t="n">
         <v>2971</v>
@@ -4396,7 +4414,7 @@
         <v>4420</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>12</v>
@@ -4410,7 +4428,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B158" s="1" t="n">
         <v>8387</v>
@@ -4447,7 +4465,7 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B160" s="1" t="n">
         <v>6756</v>
@@ -4455,7 +4473,7 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B161" s="1" t="n">
         <v>3350</v>
@@ -4472,7 +4490,7 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B162" s="1" t="n">
         <v>5868</v>
@@ -4489,13 +4507,13 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B163" s="1" t="n">
         <v>3413</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>98</v>
@@ -4506,7 +4524,7 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B164" s="1" t="n">
         <v>2790</v>
@@ -4514,7 +4532,7 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B165" s="1" t="n">
         <v>503</v>
@@ -4522,7 +4540,7 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B166" s="1" t="n">
         <v>1220</v>
@@ -4530,7 +4548,7 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B167" s="1" t="n">
         <v>12999</v>
@@ -4538,7 +4556,7 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B168" s="1" t="n">
         <v>1242</v>
@@ -4546,7 +4564,7 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B169" s="1" t="n">
         <v>282</v>
@@ -4554,7 +4572,7 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B170" s="1" t="n">
         <v>219</v>
@@ -4562,7 +4580,7 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B171" s="1" t="n">
         <v>655</v>
@@ -4570,7 +4588,7 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B172" s="1" t="n">
         <v>4150</v>
@@ -4578,7 +4596,7 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B173" s="1" t="n">
         <v>451</v>
@@ -4586,7 +4604,7 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B174" s="1" t="n">
         <v>9490</v>
@@ -4594,7 +4612,7 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B175" s="1" t="n">
         <v>1192</v>
@@ -4602,7 +4620,7 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B176" s="1" t="n">
         <v>1226</v>
@@ -4618,7 +4636,7 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B178" s="1" t="n">
         <v>19990</v>
@@ -4626,7 +4644,7 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B179" s="1" t="n">
         <v>1490</v>
@@ -4634,7 +4652,7 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B180" s="1" t="n">
         <v>3210</v>
@@ -4642,7 +4660,7 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B181" s="1" t="n">
         <v>4180</v>
@@ -4650,7 +4668,7 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B182" s="1" t="n">
         <v>1290</v>
@@ -4658,7 +4676,7 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B183" s="1" t="n">
         <v>2381</v>
@@ -4666,7 +4684,7 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B184" s="1" t="n">
         <v>943</v>
@@ -4674,7 +4692,7 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B185" s="1" t="n">
         <v>4090</v>
@@ -4682,7 +4700,7 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B186" s="1" t="n">
         <v>399</v>
@@ -4690,7 +4708,7 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B187" s="1" t="n">
         <v>340</v>
@@ -4698,7 +4716,7 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B188" s="1" t="n">
         <v>3120</v>
@@ -4706,7 +4724,7 @@
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B189" s="1" t="n">
         <v>1790</v>
@@ -4714,7 +4732,7 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B190" s="1" t="n">
         <v>425</v>
@@ -4722,7 +4740,7 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B191" s="1" t="n">
         <v>21990</v>
@@ -4730,7 +4748,7 @@
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B192" s="1" t="n">
         <v>1193</v>
@@ -4738,7 +4756,7 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B193" s="1" t="n">
         <v>2890</v>
@@ -4746,7 +4764,7 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B194" s="1" t="n">
         <v>3120</v>
@@ -4754,7 +4772,7 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B195" s="1" t="n">
         <v>1236</v>
@@ -4762,7 +4780,7 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B196" s="1" t="n">
         <v>790</v>
@@ -4770,7 +4788,7 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B197" s="1" t="n">
         <v>934</v>
@@ -4778,7 +4796,7 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B198" s="1" t="n">
         <v>590</v>
@@ -4786,7 +4804,7 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B199" s="1" t="n">
         <v>1171</v>
@@ -4794,7 +4812,7 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B200" s="1" t="n">
         <v>4120</v>
@@ -4802,7 +4820,7 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B201" s="1" t="n">
         <v>490</v>
@@ -4810,7 +4828,7 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B202" s="1" t="n">
         <v>2085</v>
@@ -4818,7 +4836,7 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B203" s="1" t="n">
         <v>1219</v>
@@ -4826,7 +4844,7 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B204" s="1" t="n">
         <v>399</v>
@@ -4834,7 +4852,7 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B205" s="1" t="n">
         <v>755</v>
@@ -4842,7 +4860,7 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B206" s="1" t="n">
         <v>2369</v>
@@ -4850,7 +4868,7 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B207" s="1" t="n">
         <v>8993</v>
@@ -4858,7 +4876,7 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B208" s="1" t="n">
         <v>2869</v>
@@ -4866,7 +4884,7 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B209" s="1" t="n">
         <v>2688</v>
@@ -4874,7 +4892,7 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B210" s="1" t="n">
         <v>5690</v>
@@ -4882,7 +4900,7 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B211" s="1" t="n">
         <v>4150</v>
@@ -4890,7 +4908,7 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B212" s="1" t="n">
         <v>690</v>
@@ -4898,7 +4916,7 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B213" s="1" t="n">
         <v>990</v>
@@ -4906,7 +4924,7 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B214" s="1" t="n">
         <v>1090</v>
@@ -4914,7 +4932,7 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B215" s="1" t="n">
         <v>1460</v>
@@ -4922,7 +4940,7 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B216" s="1" t="n">
         <v>364</v>
@@ -4930,7 +4948,7 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B217" s="1" t="n">
         <v>249</v>
@@ -4938,7 +4956,7 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B218" s="1" t="n">
         <v>174</v>
@@ -4946,7 +4964,7 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B219" s="1" t="n">
         <v>1020</v>
@@ -4954,7 +4972,7 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B220" s="1" t="n">
         <v>2958</v>
@@ -4962,7 +4980,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B221" s="1" t="n">
         <v>1365</v>
@@ -4970,7 +4988,7 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B222" s="1" t="n">
         <v>938</v>
@@ -4978,7 +4996,7 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B223" s="1" t="n">
         <v>8990</v>
@@ -4986,7 +5004,7 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B224" s="1" t="n">
         <v>950</v>
@@ -4994,7 +5012,7 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B225" s="1" t="n">
         <v>447</v>
@@ -5002,7 +5020,7 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B226" s="1" t="n">
         <v>12270</v>
@@ -5010,7 +5028,7 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B227" s="1" t="n">
         <v>528</v>
@@ -5018,7 +5036,7 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B228" s="1" t="n">
         <v>23640</v>
@@ -5026,7 +5044,7 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B229" s="1" t="n">
         <v>16800</v>
@@ -5034,7 +5052,7 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B230" s="1" t="n">
         <v>7690</v>
@@ -5042,7 +5060,7 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B231" s="1" t="n">
         <v>24990</v>
@@ -5050,7 +5068,7 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B232" s="1" t="n">
         <v>530</v>
@@ -5058,7 +5076,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B233" s="1" t="n">
         <v>950</v>
@@ -5066,7 +5084,7 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B234" s="1" t="n">
         <v>31595</v>
@@ -5074,7 +5092,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B235" s="1" t="n">
         <v>920</v>
@@ -5082,7 +5100,7 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B236" s="1" t="n">
         <v>3190</v>
@@ -5090,7 +5108,7 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B237" s="1" t="n">
         <v>30843</v>
@@ -5098,7 +5116,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B238" s="1" t="n">
         <v>2990</v>
@@ -5106,7 +5124,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B239" s="1" t="n">
         <v>5926</v>
@@ -5114,7 +5132,7 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B240" s="1" t="n">
         <v>30099</v>
@@ -5122,7 +5140,7 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B241" s="1" t="n">
         <v>11615</v>
@@ -5130,7 +5148,7 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B242" s="1" t="n">
         <v>1820</v>
@@ -5138,7 +5156,7 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B243" s="1" t="n">
         <v>2990</v>
@@ -5146,7 +5164,7 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B244" s="1" t="n">
         <v>104</v>
@@ -5154,7 +5172,7 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B245" s="1" t="n">
         <v>9194</v>
@@ -5162,7 +5180,7 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B246" s="1" t="n">
         <v>2958</v>
@@ -5170,7 +5188,7 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B247" s="1" t="n">
         <v>2690</v>
@@ -5178,7 +5196,7 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B248" s="1" t="n">
         <v>2859</v>
@@ -5186,7 +5204,7 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B249" s="1" t="n">
         <v>590</v>
@@ -5194,7 +5212,7 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B250" s="1" t="n">
         <v>650</v>
@@ -5202,7 +5220,7 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B251" s="1" t="n">
         <v>1162</v>
@@ -5210,7 +5228,7 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B252" s="1" t="n">
         <v>30890</v>
@@ -5218,7 +5236,7 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B253" s="1" t="n">
         <v>360</v>
@@ -5226,7 +5244,7 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B254" s="1" t="n">
         <v>370</v>
@@ -5234,7 +5252,7 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B255" s="1" t="n">
         <v>360</v>
@@ -5242,7 +5260,7 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B256" s="1" t="n">
         <v>420</v>
@@ -5250,7 +5268,7 @@
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B257" s="1" t="n">
         <v>5490</v>
@@ -5258,7 +5276,7 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B258" s="1" t="n">
         <v>2090</v>
@@ -5266,7 +5284,7 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B259" s="1" t="n">
         <v>25690</v>
@@ -5274,7 +5292,7 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B260" s="1" t="n">
         <v>2834</v>
@@ -5282,7 +5300,7 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B261" s="1" t="n">
         <v>1590</v>
@@ -5290,7 +5308,7 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B262" s="1" t="n">
         <v>2753</v>
@@ -5298,7 +5316,7 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B263" s="1" t="n">
         <v>18348</v>
@@ -5306,7 +5324,7 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B264" s="1" t="n">
         <v>38140</v>
@@ -5314,7 +5332,7 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B265" s="1" t="n">
         <v>178</v>
@@ -5322,7 +5340,7 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B266" s="1" t="n">
         <v>5290</v>
@@ -5330,7 +5348,7 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B267" s="1" t="n">
         <v>1553</v>
@@ -5338,7 +5356,7 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B268" s="1" t="n">
         <v>18290</v>
@@ -5346,7 +5364,7 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B269" s="1" t="n">
         <v>2050</v>
@@ -5354,7 +5372,7 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B270" s="1" t="n">
         <v>32590</v>
@@ -5362,7 +5380,7 @@
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B271" s="1" t="n">
         <v>31600</v>
@@ -5370,7 +5388,7 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B272" s="1" t="n">
         <v>63490</v>
@@ -5378,7 +5396,7 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B273" s="1" t="n">
         <v>31170</v>
@@ -5386,7 +5404,7 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B274" s="1" t="n">
         <v>21240</v>
@@ -5394,7 +5412,7 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B275" s="1" t="n">
         <v>4390</v>
@@ -5402,7 +5420,7 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B276" s="1" t="n">
         <v>2980</v>
@@ -5410,7 +5428,7 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B277" s="1" t="n">
         <v>8694</v>
@@ -5418,7 +5436,7 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B278" s="1" t="n">
         <v>4990</v>
@@ -5426,7 +5444,7 @@
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B279" s="1" t="n">
         <v>1690</v>
@@ -5434,7 +5452,7 @@
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B280" s="1" t="n">
         <v>1408</v>
@@ -5442,7 +5460,7 @@
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B281" s="1" t="n">
         <v>5990</v>
@@ -5450,7 +5468,7 @@
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B282" s="1" t="n">
         <v>1799</v>
@@ -5458,7 +5476,7 @@
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B283" s="1" t="n">
         <v>5313</v>
@@ -5466,7 +5484,7 @@
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B284" s="1" t="n">
         <v>981</v>
@@ -5474,7 +5492,7 @@
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B285" s="1" t="n">
         <v>899</v>
@@ -5482,7 +5500,7 @@
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B286" s="1" t="n">
         <v>137</v>
@@ -5490,7 +5508,7 @@
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B287" s="1" t="n">
         <v>5550</v>
@@ -5498,7 +5516,7 @@
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B288" s="1" t="n">
         <v>1495</v>
@@ -5506,7 +5524,7 @@
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B289" s="1" t="n">
         <v>1290</v>
@@ -5514,7 +5532,7 @@
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B290" s="1" t="n">
         <v>1290</v>
@@ -5522,7 +5540,7 @@
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B291" s="1" t="n">
         <v>7190</v>
@@ -5530,7 +5548,7 @@
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B292" s="1" t="n">
         <v>890</v>
@@ -5538,7 +5556,7 @@
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B293" s="1" t="n">
         <v>305</v>
@@ -5546,7 +5564,7 @@
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B294" s="1" t="n">
         <v>307</v>
@@ -5554,7 +5572,7 @@
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B295" s="1" t="n">
         <v>1291</v>
@@ -5562,7 +5580,7 @@
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B296" s="1" t="n">
         <v>7190</v>
@@ -5570,7 +5588,7 @@
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B297" s="1" t="n">
         <v>4390</v>
@@ -5578,7 +5596,7 @@
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B298" s="1" t="n">
         <v>400</v>
@@ -5586,7 +5604,7 @@
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B299" s="1" t="n">
         <v>1603</v>
@@ -5594,7 +5612,7 @@
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B300" s="1" t="n">
         <v>1454</v>
@@ -5602,7 +5620,7 @@
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B301" s="1" t="n">
         <v>4290</v>
@@ -5610,7 +5628,7 @@
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B302" s="1" t="n">
         <v>1990</v>
@@ -5618,7 +5636,7 @@
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B303" s="1" t="n">
         <v>4190</v>
@@ -5626,7 +5644,7 @@
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B304" s="1" t="n">
         <v>21440</v>
@@ -5634,7 +5652,7 @@
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B305" s="1" t="n">
         <v>2958</v>
@@ -5642,7 +5660,7 @@
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B306" s="1" t="n">
         <v>2933</v>
@@ -5650,7 +5668,7 @@
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B307" s="1" t="n">
         <v>241</v>
@@ -5658,7 +5676,7 @@
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B308" s="1" t="n">
         <v>26790</v>
@@ -5666,7 +5684,7 @@
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B309" s="1" t="n">
         <v>5470</v>
@@ -5674,7 +5692,7 @@
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B310" s="1" t="n">
         <v>2280</v>
@@ -5682,7 +5700,7 @@
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B311" s="1" t="n">
         <v>996</v>
@@ -5690,7 +5708,7 @@
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B312" s="1" t="n">
         <v>24600</v>
@@ -5698,7 +5716,7 @@
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B313" s="1" t="n">
         <v>28290</v>
@@ -5706,7 +5724,7 @@
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B314" s="1" t="n">
         <v>566</v>
@@ -5714,7 +5732,7 @@
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B315" s="1" t="n">
         <v>1490</v>
@@ -5722,7 +5740,7 @@
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B316" s="1" t="n">
         <v>768</v>
@@ -5730,7 +5748,7 @@
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B317" s="1" t="n">
         <v>3990</v>
@@ -5738,7 +5756,7 @@
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B318" s="1" t="n">
         <v>3086</v>
@@ -5746,7 +5764,7 @@
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B319" s="1" t="n">
         <v>20890</v>
@@ -5754,7 +5772,7 @@
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B320" s="1" t="n">
         <v>2990</v>
@@ -5770,7 +5788,7 @@
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B322" s="1" t="n">
         <v>17967</v>
@@ -5778,7 +5796,7 @@
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B323" s="1" t="n">
         <v>22190</v>
@@ -5786,7 +5804,7 @@
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B324" s="1" t="n">
         <v>43990</v>
@@ -5794,7 +5812,7 @@
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B325" s="1" t="n">
         <v>1690</v>
@@ -5802,7 +5820,7 @@
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B326" s="1" t="n">
         <v>30510</v>
@@ -5810,7 +5828,7 @@
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B327" s="1" t="n">
         <v>6390</v>
@@ -5818,7 +5836,7 @@
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B328" s="1" t="n">
         <v>4190</v>
@@ -5826,7 +5844,7 @@
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B329" s="1" t="n">
         <v>30510</v>
@@ -5834,7 +5852,7 @@
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B330" s="1" t="n">
         <v>850</v>
@@ -5850,7 +5868,7 @@
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B332" s="1" t="n">
         <v>33490</v>
@@ -5858,7 +5876,7 @@
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B333" s="1" t="n">
         <v>11900</v>
@@ -5866,7 +5884,7 @@
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B334" s="1" t="n">
         <v>5650</v>
@@ -5874,7 +5892,7 @@
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B335" s="1" t="n">
         <v>1007</v>
@@ -5882,7 +5900,7 @@
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B336" s="1" t="n">
         <v>1148</v>
@@ -5890,7 +5908,7 @@
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B337" s="1" t="n">
         <v>27410</v>
@@ -5906,7 +5924,7 @@
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B339" s="1" t="n">
         <v>8990</v>
@@ -5914,7 +5932,7 @@
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B340" s="1" t="n">
         <v>646</v>
@@ -5922,7 +5940,7 @@
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B341" s="1" t="n">
         <v>2004</v>
@@ -5930,7 +5948,7 @@
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B342" s="1" t="n">
         <v>1263</v>
@@ -5938,7 +5956,7 @@
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B343" s="1" t="n">
         <v>4893</v>
@@ -5946,7 +5964,7 @@
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B344" s="1" t="n">
         <v>780</v>
@@ -5954,13 +5972,13 @@
     </row>
     <row r="345" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B345" s="1" t="n">
         <v>4097</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D345" s="1" t="s">
         <v>98</v>
@@ -5971,7 +5989,7 @@
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B346" s="1" t="n">
         <v>1590</v>
@@ -5979,7 +5997,7 @@
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B347" s="1" t="n">
         <v>26990</v>
@@ -5987,7 +6005,7 @@
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B348" s="1" t="n">
         <v>68790</v>
@@ -5995,7 +6013,7 @@
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B349" s="1" t="n">
         <v>1936</v>
@@ -6003,7 +6021,7 @@
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B350" s="1" t="n">
         <v>19610</v>
@@ -6011,7 +6029,7 @@
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B351" s="1" t="n">
         <v>38700</v>
@@ -6019,7 +6037,7 @@
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B352" s="1" t="n">
         <v>4290</v>
@@ -6027,7 +6045,7 @@
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B353" s="1" t="n">
         <v>8590</v>
@@ -6035,7 +6053,7 @@
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B354" s="1" t="n">
         <v>31390</v>
@@ -6043,7 +6061,7 @@
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B355" s="1" t="n">
         <v>41450</v>
@@ -6051,7 +6069,7 @@
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B356" s="1" t="n">
         <v>759</v>
@@ -6059,7 +6077,7 @@
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B357" s="1" t="n">
         <v>1518</v>
@@ -6067,7 +6085,7 @@
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B358" s="1" t="n">
         <v>61</v>
@@ -6075,7 +6093,7 @@
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B359" s="1" t="n">
         <v>1490</v>
@@ -6083,7 +6101,7 @@
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B360" s="1" t="n">
         <v>12282</v>
@@ -6091,7 +6109,7 @@
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B361" s="1" t="n">
         <v>344</v>
@@ -6099,7 +6117,7 @@
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B362" s="1" t="n">
         <v>1470</v>
@@ -6107,7 +6125,7 @@
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B363" s="1" t="n">
         <v>1896</v>
@@ -6115,7 +6133,7 @@
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B364" s="1" t="n">
         <v>42990</v>
@@ -6123,7 +6141,7 @@
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B365" s="1" t="n">
         <v>7289</v>
@@ -6131,7 +6149,7 @@
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B366" s="1" t="n">
         <v>590</v>
@@ -6139,7 +6157,7 @@
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B367" s="1" t="n">
         <v>35470</v>
@@ -6155,7 +6173,7 @@
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B369" s="1" t="n">
         <v>3590</v>
@@ -6163,7 +6181,7 @@
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B370" s="1" t="n">
         <v>19890</v>
@@ -6171,7 +6189,7 @@
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B371" s="1" t="n">
         <v>590</v>
@@ -6179,7 +6197,7 @@
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B372" s="1" t="n">
         <v>703</v>
@@ -6187,7 +6205,7 @@
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B373" s="1" t="n">
         <v>50510</v>
@@ -6195,7 +6213,7 @@
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B374" s="1" t="n">
         <v>720</v>
@@ -6203,7 +6221,7 @@
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B375" s="1" t="n">
         <v>1770</v>
@@ -6211,7 +6229,7 @@
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B376" s="1" t="n">
         <v>9390</v>
@@ -6219,7 +6237,7 @@
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B377" s="1" t="n">
         <v>6836</v>
@@ -6227,7 +6245,7 @@
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B378" s="1" t="n">
         <v>5540</v>
@@ -6235,7 +6253,7 @@
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B379" s="1" t="n">
         <v>2643</v>
@@ -6243,7 +6261,7 @@
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B380" s="1" t="n">
         <v>10905</v>
@@ -6251,7 +6269,7 @@
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B381" s="1" t="n">
         <v>1603</v>
@@ -6259,7 +6277,7 @@
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B382" s="1" t="n">
         <v>7190</v>
@@ -6267,7 +6285,7 @@
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B383" s="1" t="n">
         <v>35960</v>
@@ -6275,7 +6293,7 @@
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B384" s="1" t="n">
         <v>4190</v>
@@ -6283,7 +6301,7 @@
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B385" s="1" t="n">
         <v>1090</v>
@@ -6291,7 +6309,7 @@
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B386" s="1" t="n">
         <v>930</v>
@@ -6299,7 +6317,7 @@
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B387" s="1" t="n">
         <v>1190</v>
@@ -6307,7 +6325,7 @@
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B388" s="1" t="n">
         <v>31790</v>
@@ -6315,7 +6333,7 @@
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B389" s="1" t="n">
         <v>723</v>
@@ -6323,7 +6341,7 @@
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B390" s="1" t="n">
         <v>921</v>
@@ -6331,7 +6349,7 @@
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B391" s="1" t="n">
         <v>540</v>
@@ -6339,7 +6357,7 @@
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B392" s="1" t="n">
         <v>45770</v>
@@ -6347,7 +6365,7 @@
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B393" s="1" t="n">
         <v>26890</v>
@@ -6355,7 +6373,7 @@
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B394" s="1" t="n">
         <v>2280</v>
@@ -6363,7 +6381,7 @@
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B395" s="1" t="n">
         <v>2404</v>
@@ -6371,7 +6389,7 @@
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B396" s="1" t="n">
         <v>10900</v>
@@ -6379,7 +6397,7 @@
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B397" s="1" t="n">
         <v>807</v>
@@ -6387,7 +6405,7 @@
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B398" s="1" t="n">
         <v>2290</v>
@@ -6395,7 +6413,7 @@
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B399" s="1" t="n">
         <v>20700</v>
@@ -6403,7 +6421,7 @@
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B400" s="1" t="n">
         <v>3731</v>
@@ -6411,7 +6429,7 @@
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B401" s="1" t="n">
         <v>2190</v>
@@ -6419,7 +6437,7 @@
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B402" s="1" t="n">
         <v>890</v>
@@ -6427,7 +6445,7 @@
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B403" s="1" t="n">
         <v>8890</v>
@@ -6435,7 +6453,7 @@
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B404" s="1" t="n">
         <v>18590</v>
@@ -6443,7 +6461,7 @@
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B405" s="1" t="n">
         <v>25723</v>
@@ -6451,7 +6469,7 @@
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B406" s="1" t="n">
         <v>1208</v>
@@ -6459,13 +6477,13 @@
     </row>
     <row r="407" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B407" s="1" t="n">
         <v>3201</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D407" s="1" t="s">
         <v>98</v>
@@ -6476,7 +6494,7 @@
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B408" s="1" t="n">
         <v>1162</v>
@@ -6484,7 +6502,7 @@
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B409" s="1" t="n">
         <v>1590</v>
@@ -6492,7 +6510,7 @@
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B410" s="1" t="n">
         <v>194</v>
@@ -6500,7 +6518,7 @@
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B411" s="1" t="n">
         <v>26870</v>
@@ -6508,7 +6526,7 @@
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B412" s="1" t="n">
         <v>21800</v>
@@ -6516,13 +6534,13 @@
     </row>
     <row r="413" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B413" s="1" t="n">
         <v>3070</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D413" s="1" t="s">
         <v>98</v>
@@ -6541,7 +6559,7 @@
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B415" s="1" t="n">
         <v>27240</v>
@@ -6549,7 +6567,7 @@
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B416" s="1" t="n">
         <v>31060</v>
@@ -6557,7 +6575,7 @@
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B417" s="1" t="n">
         <v>874</v>
@@ -6565,7 +6583,7 @@
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B418" s="1" t="n">
         <v>5690</v>
@@ -6573,7 +6591,7 @@
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B419" s="1" t="n">
         <v>341</v>
@@ -6581,7 +6599,7 @@
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B420" s="1" t="n">
         <v>1377</v>
@@ -6589,7 +6607,7 @@
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B421" s="1" t="n">
         <v>3972</v>
@@ -6597,7 +6615,7 @@
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B422" s="1" t="n">
         <v>210</v>
@@ -6613,13 +6631,13 @@
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B424" s="1" t="n">
         <v>2790</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D424" s="3" t="n">
         <v>46248</v>
@@ -6630,7 +6648,7 @@
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B425" s="1" t="n">
         <v>47490</v>
@@ -6638,7 +6656,7 @@
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B426" s="1" t="n">
         <v>10190</v>
@@ -6646,7 +6664,7 @@
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B427" s="1" t="n">
         <v>2090</v>
@@ -6654,7 +6672,7 @@
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B428" s="1" t="n">
         <v>370</v>
@@ -6662,7 +6680,7 @@
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B429" s="1" t="n">
         <v>1432</v>
@@ -6670,7 +6688,7 @@
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B430" s="1" t="n">
         <v>85990</v>
@@ -6678,7 +6696,7 @@
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B431" s="1" t="n">
         <v>5730</v>
@@ -6698,7 +6716,7 @@
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B432" s="1" t="n">
         <v>6950</v>
@@ -6706,7 +6724,7 @@
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B433" s="1" t="n">
         <v>25090</v>
@@ -6714,7 +6732,7 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B434" s="1" t="n">
         <v>25766</v>
@@ -6722,7 +6740,7 @@
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B435" s="1" t="n">
         <v>9490</v>
@@ -6730,7 +6748,7 @@
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B436" s="1" t="n">
         <v>2890</v>
@@ -6738,7 +6756,7 @@
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B437" s="1" t="n">
         <v>2790</v>
@@ -6746,7 +6764,7 @@
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B438" s="1" t="n">
         <v>890</v>
@@ -6754,7 +6772,7 @@
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B439" s="1" t="n">
         <v>3230</v>
@@ -6762,7 +6780,7 @@
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B440" s="1" t="n">
         <v>27450</v>
@@ -6770,7 +6788,7 @@
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B441" s="1" t="n">
         <v>3190</v>
@@ -6778,7 +6796,7 @@
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B442" s="1" t="n">
         <v>4950</v>
@@ -6786,7 +6804,7 @@
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B443" s="1" t="n">
         <v>2490</v>
@@ -6794,7 +6812,7 @@
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B444" s="1" t="n">
         <v>5619</v>
@@ -6802,7 +6820,7 @@
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B445" s="1" t="n">
         <v>2490</v>
@@ -6810,7 +6828,7 @@
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B446" s="1" t="n">
         <v>13590</v>
@@ -6818,7 +6836,7 @@
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B447" s="1" t="n">
         <v>2166</v>
@@ -6826,7 +6844,7 @@
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B448" s="1" t="n">
         <v>6683</v>
@@ -6834,7 +6852,7 @@
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B449" s="1" t="n">
         <v>42490</v>
@@ -6842,7 +6860,7 @@
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B450" s="1" t="n">
         <v>139</v>
@@ -6858,7 +6876,7 @@
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B452" s="1" t="n">
         <v>3450</v>
@@ -6866,7 +6884,7 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B453" s="1" t="n">
         <v>3972</v>
@@ -6874,7 +6892,7 @@
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B454" s="1" t="n">
         <v>3990</v>
@@ -6882,7 +6900,7 @@
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B455" s="1" t="n">
         <v>1190</v>
@@ -6890,7 +6908,7 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B456" s="1" t="n">
         <v>2990</v>
@@ -6898,7 +6916,7 @@
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B457" s="1" t="n">
         <v>2383</v>
@@ -6914,7 +6932,7 @@
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B459" s="1" t="n">
         <v>4290</v>
@@ -6922,7 +6940,7 @@
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B460" s="1" t="n">
         <v>298</v>
@@ -6930,7 +6948,7 @@
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B461" s="1" t="n">
         <v>295</v>
@@ -6938,7 +6956,7 @@
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B462" s="1" t="n">
         <v>1250</v>
@@ -6946,7 +6964,7 @@
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B463" s="1" t="n">
         <v>2390</v>
@@ -6970,7 +6988,7 @@
     </row>
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B466" s="1" t="n">
         <v>77</v>
@@ -6978,7 +6996,7 @@
     </row>
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B467" s="1" t="n">
         <v>16999</v>
@@ -6986,13 +7004,13 @@
     </row>
     <row r="468" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B468" s="1" t="n">
         <v>8154</v>
       </c>
       <c r="C468" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D468" s="1" t="s">
         <v>98</v>
@@ -7003,7 +7021,7 @@
     </row>
     <row r="469" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B469" s="1" t="n">
         <v>32690</v>
@@ -7011,7 +7029,7 @@
     </row>
     <row r="470" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B470" s="1" t="n">
         <v>807</v>
@@ -7019,7 +7037,7 @@
     </row>
     <row r="471" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B471" s="1" t="n">
         <v>341</v>
@@ -7027,7 +7045,7 @@
     </row>
     <row r="472" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B472" s="1" t="n">
         <v>282</v>
@@ -7035,7 +7053,7 @@
     </row>
     <row r="473" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B473" s="1" t="n">
         <v>1377</v>
@@ -7043,7 +7061,7 @@
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B474" s="1" t="n">
         <v>1850</v>
@@ -7051,7 +7069,7 @@
     </row>
     <row r="475" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B475" s="1" t="n">
         <v>69990</v>
@@ -7059,7 +7077,7 @@
     </row>
     <row r="476" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B476" s="1" t="n">
         <v>26100</v>
@@ -7067,7 +7085,7 @@
     </row>
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B477" s="1" t="n">
         <v>1790</v>
@@ -7075,13 +7093,13 @@
     </row>
     <row r="478" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B478" s="1" t="n">
         <v>5514</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D478" s="1" t="s">
         <v>12</v>
@@ -7095,7 +7113,7 @@
     </row>
     <row r="479" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B479" s="1" t="n">
         <v>396</v>
@@ -7103,7 +7121,7 @@
     </row>
     <row r="480" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B480" s="1" t="n">
         <v>1890</v>
@@ -7111,7 +7129,7 @@
     </row>
     <row r="481" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B481" s="1" t="n">
         <v>30690</v>
@@ -7119,7 +7137,7 @@
     </row>
     <row r="482" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B482" s="1" t="n">
         <v>26900</v>
@@ -7127,7 +7145,7 @@
     </row>
     <row r="483" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B483" s="1" t="n">
         <v>2990</v>
@@ -7143,7 +7161,7 @@
     </row>
     <row r="485" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B485" s="1" t="n">
         <v>1762</v>
@@ -7151,7 +7169,7 @@
     </row>
     <row r="486" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B486" s="1" t="n">
         <v>240</v>
@@ -7159,7 +7177,7 @@
     </row>
     <row r="487" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B487" s="1" t="n">
         <v>3890</v>
@@ -7167,7 +7185,7 @@
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B488" s="1" t="n">
         <v>6690</v>
@@ -7175,7 +7193,7 @@
     </row>
     <row r="489" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B489" s="1" t="n">
         <v>5085</v>
@@ -7183,7 +7201,7 @@
     </row>
     <row r="490" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B490" s="1" t="n">
         <v>41410</v>
@@ -7191,7 +7209,7 @@
     </row>
     <row r="491" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B491" s="1" t="n">
         <v>4321</v>
@@ -7199,7 +7217,7 @@
     </row>
     <row r="492" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B492" s="1" t="n">
         <v>15857</v>
@@ -7207,7 +7225,7 @@
     </row>
     <row r="493" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B493" s="1" t="n">
         <v>29490</v>
@@ -7215,7 +7233,7 @@
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B494" s="1" t="n">
         <v>550</v>
@@ -7223,7 +7241,7 @@
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B495" s="1" t="n">
         <v>2460</v>
@@ -7231,7 +7249,7 @@
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B496" s="1" t="n">
         <v>12939</v>
@@ -7239,7 +7257,7 @@
     </row>
     <row r="497" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B497" s="1" t="n">
         <v>447</v>
@@ -7247,7 +7265,7 @@
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B498" s="1" t="n">
         <v>8799</v>
@@ -7255,7 +7273,7 @@
     </row>
     <row r="499" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B499" s="1" t="n">
         <v>780</v>
@@ -7263,7 +7281,7 @@
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B500" s="1" t="n">
         <v>196882</v>
@@ -7271,7 +7289,7 @@
     </row>
     <row r="501" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B501" s="1" t="n">
         <v>3364</v>
@@ -7279,7 +7297,7 @@
     </row>
     <row r="502" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B502" s="1" t="n">
         <v>8390</v>
@@ -7287,7 +7305,7 @@
     </row>
     <row r="503" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A503" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B503" s="1" t="n">
         <v>213</v>
@@ -7295,7 +7313,7 @@
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B504" s="1" t="n">
         <v>810</v>
